--- a/docs/deliverables/out/Drop-1_Transactional/BRD-12_Submitted_Policies/BIBS_TestPlan_BRD-12_Submitted_Policies_v1.0.xlsx
+++ b/docs/deliverables/out/Drop-1_Transactional/BRD-12_Submitted_Policies/BIBS_TestPlan_BRD-12_Submitted_Policies_v1.0.xlsx
@@ -16,11 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles and Access" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRS Findings" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_lists" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_lists" sheetId="10" state="hidden" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$65</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Document Control'!$A$4:$F$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Document Control'!$4:$4</definedName>
@@ -28,16 +27,14 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Test Conditions'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Scenarios'!$A$4:$F$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Scenarios'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Cases'!$A$4:$R$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Cases'!$A$4:$Q$126</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Test Cases'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Coverage'!$A$4:$J$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Coverage'!$A$4:$I$68</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Coverage'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Test Data'!$A$4:$E$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Test Data'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Roles and Access'!$A$4:$M$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Roles and Access'!$A$4:$L$81</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Roles and Access'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'FRS Findings'!$A$4:$D$14</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'FRS Findings'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,7 +435,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="971550" cy="285750"/>
@@ -751,7 +748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E39"/>
+  <dimension ref="B4:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1010,92 +1007,77 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>FRS points raised for the FRS owner; the affected cases assume the proposed resolution</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="n">
-        <v>10</v>
+    <row r="29">
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>Legend</t>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>The case ran and the actual result matches the expected result</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>The case ran and the actual result matches the expected result</t>
+          <t>The actual result differs; an issue ID is recorded</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
-          <t>The actual result differs; a defect ID is recorded</t>
+          <t>The case cannot run (environment, data or an open issue elsewhere)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
-          <t>The case cannot run (environment, data or a defect elsewhere)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
           <t>Not applicable in this cycle, with the reason in Actual result</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>Source: FRS BRD-12 Submitted Policies. 31 FRs, 33 BRD IDs, 94 test conditions, 9 scenarios, 122 test cases (58 positive, 64 negative).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>Source: FRS BRD-12 (FRS_BRD12_SUBMITTED_POLICIES.md). 31 FRs, 33 BRD IDs, 94 test conditions, 9 scenarios, 122 test cases (58 positive, 64 negative), 0 with an automation reference.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="19" t="inlineStr">
-        <is>
-          <t>Status starts as Not run. Testers fill Status, Actual result, Tester, Date and Defect ID during execution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="26" customHeight="1">
-      <c r="B39" s="20" t="inlineStr">
+          <t>Status starts as Not run. Testers fill Status, Actual result, Tester, Date and Issue ID during execution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>Prepared by iorta TechNXT for BDOI. Confidential – BDOI.</t>
         </is>
@@ -1111,7 +1093,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId9"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -1124,7 +1105,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
 </worksheet>
 </file>
 
@@ -1132,310 +1113,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>FRS points raised for the FRS owner; the affected cases assume the proposed resolution</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="6" customHeight="1">
-      <c r="A3" s="25" t="n"/>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B4" s="26" t="inlineStr">
-        <is>
-          <t>FR ID</t>
-        </is>
-      </c>
-      <c r="C4" s="26" t="inlineStr">
-        <is>
-          <t>Finding</t>
-        </is>
-      </c>
-      <c r="D4" s="26" t="inlineStr">
-        <is>
-          <t>Proposed resolution</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>TF-SP-01</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>FR-SP-001</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>The natural key includes the expiry date, so a row for the next term of the same policy creates a new record, while acceptance criterion 3 speaks of "a row updating an existing policy". The FRS does not say which fields may change on an update and which make a new record.</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>List the fields that update a record and state that a new expiry date makes a new term record linked to the previous one.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>TF-SP-02</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>FR-SP-030</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>The default classification uses "BDOI did not place the policy", which is not a field of the masterlist or LAMD; the definition is open (SP SQ04).</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Name the data element that tells whether BDOI placed the policy; the cases test the PN match only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>TF-SP-03</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>FR-SP-031</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Bucket precedence and the RMU / FFY conflicts are open (SP SQ05) and the conflicting rules are seeded inactive, so a record that is both FFY and RMU cannot be tested.</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Answer SP SQ05 and add the precedence to the FRS; a case is added then.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>TF-SP-04</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>FR-SP-032</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>The rule that chooses the Generic or the FFY RA is to be confirmed (SP SQ06); the cases follow the seed rule.</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>State the rule in the FRS when SP SQ06 is answered.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>TF-SP-05</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>FR-SP-040</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>The FRS keeps one IAAF per policy with links, while the BRD's current process lets one IAAF cover several policies (SP SQ07). The bank counterpart may expect one form.</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Confirm with BDOI; the cases test one IAAF per policy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>TF-SP-06</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>FR-SP-053</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>The meaning of Released is to be confirmed (SP SQ08); the default is the AO's first opening, which a preview by another user could not trigger but a download by the assigned AO does.</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Define Released (first opening, first download or explicit acknowledgement) in the FRS.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>TF-SP-07</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>FR-SP-062</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>The owner of the renewal notice and renewal proposal letters is not confirmed (XQ03); the cases may move to the BRD-6 plan.</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Record the owner after XQ03; the cases here test the reminder letter and the print batch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>TF-SP-08</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>FR-SP-063</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>The BRD gives an acceptance window of 3-5 days; the FRS default is 5 (SP SQ12). The FRS does not say whether days are calendar or working days.</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>State calendar or working days; the boundary cases use calendar days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>TF-SP-09</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>FR-SP-070</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>Amount, VAT, OR and GL account of the handling fee are to be confirmed (SP SQ13), so the accounting of the applied payment cannot be checked.</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Add the accounting entry to the FRS after SP SQ13; the cases check tagging and the OR only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>TF-SP-10</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>FR-SP-080</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>BRIDSP-30 repeats BRIDSP-20 word for word; the FRS traces both to one FR, which inflates the BRD ID count.</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Ask the BRD owner to confirm that BRIDSP-30 is a duplicate and mark it so in the traceability.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:D14"/>
-  <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="A5:D514">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Test Plan BRD-12 Submitted Policies&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
-    <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1584,6 +1264,20 @@
       <c r="B7" t="inlineStr">
         <is>
           <t>Upload-download</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Message</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2079,7 +1773,7 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>Positive, Negative, Boundary, Security-access, Workflow, Report-output, Upload-download</t>
+          <t>Positive, Negative, Boundary, Security-access, Workflow, Report-output, Upload-download, Screen, Message</t>
         </is>
       </c>
     </row>
@@ -2096,7 +1790,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Role code and name (and SIT/UAT user for built BRDs)</t>
+          <t>Role code and name (and the SIT/UAT user)</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr"/>
@@ -2168,7 +1862,7 @@
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>What the system must do, with the exact message text and, for built BRDs, its code</t>
+          <t>What the system must do, with the exact message text and, where the system shows one, its code</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr"/>
@@ -2203,15 +1897,19 @@
       </c>
       <c r="B35" s="22" t="inlineStr">
         <is>
-          <t>Automation reference</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Existing automated test (class#method) that covers the case; blank when none</t>
-        </is>
-      </c>
-      <c r="D35" s="12" t="inlineStr"/>
+          <t>Execution status</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>Not run, Pass, Fail, Blocked, N/A</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -2221,19 +1919,15 @@
       </c>
       <c r="B36" s="23" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Actual result</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Execution status</t>
-        </is>
-      </c>
-      <c r="D36" s="14" t="inlineStr">
-        <is>
-          <t>Not run, Pass, Fail, Blocked, N/A</t>
-        </is>
-      </c>
+          <t>What happened, filled by the tester</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
@@ -2243,12 +1937,12 @@
       </c>
       <c r="B37" s="22" t="inlineStr">
         <is>
-          <t>Actual result</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>What happened, filled by the tester</t>
+          <t>Who ran the case</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr"/>
@@ -2261,12 +1955,12 @@
       </c>
       <c r="B38" s="23" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Who ran the case</t>
+          <t>Date of the run</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr"/>
@@ -2279,12 +1973,12 @@
       </c>
       <c r="B39" s="22" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Issue ID</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Date of the run</t>
+          <t>Issue raised when the case fails</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr"/>
@@ -2292,17 +1986,17 @@
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>Test Cases</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="B40" s="23" t="inlineStr">
         <is>
-          <t>Defect ID</t>
+          <t>FR / BRD ID</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Defect raised when the case fails</t>
+          <t>FR of the FRS, then BRD requirement ID</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr"/>
@@ -2315,12 +2009,12 @@
       </c>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>FR / BRD ID</t>
+          <t>Kind</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>FR of the FRS, then BRD requirement ID</t>
+          <t>FR or BRD ID</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr"/>
@@ -2333,12 +2027,12 @@
       </c>
       <c r="B42" s="23" t="inlineStr">
         <is>
-          <t>Kind</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>FR or BRD ID</t>
+          <t>FR title</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr"/>
@@ -2351,12 +2045,12 @@
       </c>
       <c r="B43" s="22" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Traces</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>FR title</t>
+          <t>BRD IDs of the FR, or FRs of the BRD ID</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr"/>
@@ -2369,12 +2063,12 @@
       </c>
       <c r="B44" s="23" t="inlineStr">
         <is>
-          <t>Traces</t>
+          <t>Conditions</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>BRD IDs of the FR, or FRs of the BRD ID</t>
+          <t>Test conditions</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr"/>
@@ -2387,12 +2081,12 @@
       </c>
       <c r="B45" s="22" t="inlineStr">
         <is>
-          <t>Conditions</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Test conditions</t>
+          <t>Cases where the action succeeds</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr"/>
@@ -2405,12 +2099,12 @@
       </c>
       <c r="B46" s="23" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Cases where the action succeeds</t>
+          <t>Cases where BIBS refuses the action</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr"/>
@@ -2423,12 +2117,12 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Cases where BIBS refuses the action</t>
+          <t>All cases</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr"/>
@@ -2441,30 +2135,34 @@
       </c>
       <c r="B48" s="23" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>All cases</t>
-        </is>
-      </c>
-      <c r="D48" s="14" t="inlineStr"/>
+          <t>Covered: at least one positive and one negative case (FR) or one case (BRD ID); GAP otherwise</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>Covered, GAP</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Test Data</t>
         </is>
       </c>
       <c r="B49" s="22" t="inlineStr">
         <is>
-          <t>Automated</t>
+          <t>Data set</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Cases with an automation reference</t>
+          <t>Data set ID</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr"/>
@@ -2472,24 +2170,20 @@
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Test Data</t>
         </is>
       </c>
       <c r="B50" s="23" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Covered: at least one positive and one negative case (FR) or one case (BRD ID); GAP otherwise</t>
-        </is>
-      </c>
-      <c r="D50" s="14" t="inlineStr">
-        <is>
-          <t>Covered, GAP</t>
-        </is>
-      </c>
+          <t>Short name used in the cases</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
@@ -2499,12 +2193,12 @@
       </c>
       <c r="B51" s="22" t="inlineStr">
         <is>
-          <t>Data set</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Data set ID</t>
+          <t>Records and values in the set</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr"/>
@@ -2517,12 +2211,12 @@
       </c>
       <c r="B52" s="23" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Short name used in the cases</t>
+          <t>Seed data set that provides it, or how the tester prepares it; non-production data is masked</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr"/>
@@ -2535,12 +2229,12 @@
       </c>
       <c r="B53" s="22" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Cases</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Records and values in the set</t>
+          <t>Number of cases that use it</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr"/>
@@ -2548,17 +2242,17 @@
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>Test Data</t>
+          <t>Roles and Access</t>
         </is>
       </c>
       <c r="B54" s="23" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Case ID</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
+          <t>Access case ID: AC-&lt;code&gt;-&lt;nn&gt;.&lt;n&gt;</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr"/>
@@ -2566,17 +2260,17 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>Test Data</t>
+          <t>Roles and Access</t>
         </is>
       </c>
       <c r="B55" s="22" t="inlineStr">
         <is>
-          <t>Cases</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Number of cases that use it</t>
+          <t>Screen or action checked</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr"/>
@@ -2589,12 +2283,12 @@
       </c>
       <c r="B56" s="23" t="inlineStr">
         <is>
-          <t>Case ID</t>
+          <t>Screen (menu path)</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Access case ID: AC-&lt;code&gt;-&lt;nn&gt;.&lt;n&gt;</t>
+          <t>Where it is done</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr"/>
@@ -2607,12 +2301,12 @@
       </c>
       <c r="B57" s="22" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Permission</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Screen or action checked</t>
+          <t>BIBS permission that grants it</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr"/>
@@ -2625,12 +2319,12 @@
       </c>
       <c r="B58" s="23" t="inlineStr">
         <is>
-          <t>Screen (menu path)</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Where it is done</t>
+          <t>Role tested (log in as a user who holds only this role)</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr"/>
@@ -2643,15 +2337,19 @@
       </c>
       <c r="B59" s="22" t="inlineStr">
         <is>
-          <t>Permission</t>
+          <t>Access</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>BIBS permission that grants it</t>
-        </is>
-      </c>
-      <c r="D59" s="12" t="inlineStr"/>
+          <t>Expected access</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>Allowed, Denied</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
@@ -2661,12 +2359,12 @@
       </c>
       <c r="B60" s="23" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Expected result</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Role tested (log in as a user who holds only this role)</t>
+          <t>What the user sees</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr"/>
@@ -2679,17 +2377,17 @@
       </c>
       <c r="B61" s="22" t="inlineStr">
         <is>
-          <t>Access</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Expected access</t>
+          <t>Execution status</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Allowed, Denied</t>
+          <t>Not run, Pass, Fail, Blocked, N/A</t>
         </is>
       </c>
     </row>
@@ -2701,12 +2399,12 @@
       </c>
       <c r="B62" s="23" t="inlineStr">
         <is>
-          <t>Expected result</t>
+          <t>Actual result</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>What the user sees</t>
+          <t>Filled by the tester</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr"/>
@@ -2719,12 +2417,12 @@
       </c>
       <c r="B63" s="22" t="inlineStr">
         <is>
-          <t>Automation reference</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Existing automated test, if any</t>
+          <t>Who ran the case</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr"/>
@@ -2737,19 +2435,15 @@
       </c>
       <c r="B64" s="23" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Execution status</t>
-        </is>
-      </c>
-      <c r="D64" s="14" t="inlineStr">
-        <is>
-          <t>Not run, Pass, Fail, Blocked, N/A</t>
-        </is>
-      </c>
+          <t>Date of the run</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
@@ -2759,144 +2453,18 @@
       </c>
       <c r="B65" s="22" t="inlineStr">
         <is>
-          <t>Actual result</t>
+          <t>Issue ID</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Filled by the tester</t>
+          <t>Issue raised when the case fails</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr"/>
     </row>
-    <row r="66">
-      <c r="A66" s="14" t="inlineStr">
-        <is>
-          <t>Roles and Access</t>
-        </is>
-      </c>
-      <c r="B66" s="23" t="inlineStr">
-        <is>
-          <t>Tester</t>
-        </is>
-      </c>
-      <c r="C66" s="14" t="inlineStr">
-        <is>
-          <t>Who ran the case</t>
-        </is>
-      </c>
-      <c r="D66" s="14" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="12" t="inlineStr">
-        <is>
-          <t>Roles and Access</t>
-        </is>
-      </c>
-      <c r="B67" s="22" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C67" s="12" t="inlineStr">
-        <is>
-          <t>Date of the run</t>
-        </is>
-      </c>
-      <c r="D67" s="12" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="14" t="inlineStr">
-        <is>
-          <t>Roles and Access</t>
-        </is>
-      </c>
-      <c r="B68" s="23" t="inlineStr">
-        <is>
-          <t>Defect ID</t>
-        </is>
-      </c>
-      <c r="C68" s="14" t="inlineStr">
-        <is>
-          <t>Defect raised when the case fails</t>
-        </is>
-      </c>
-      <c r="D68" s="14" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="12" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="B69" s="22" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C69" s="12" t="inlineStr">
-        <is>
-          <t>Finding ID</t>
-        </is>
-      </c>
-      <c r="D69" s="12" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="14" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="B70" s="23" t="inlineStr">
-        <is>
-          <t>FR ID</t>
-        </is>
-      </c>
-      <c r="C70" s="14" t="inlineStr">
-        <is>
-          <t>FR concerned</t>
-        </is>
-      </c>
-      <c r="D70" s="14" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="12" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="B71" s="22" t="inlineStr">
-        <is>
-          <t>Finding</t>
-        </is>
-      </c>
-      <c r="C71" s="12" t="inlineStr">
-        <is>
-          <t>Ambiguous or untestable point found while writing the cases</t>
-        </is>
-      </c>
-      <c r="D71" s="12" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="14" t="inlineStr">
-        <is>
-          <t>FRS Findings</t>
-        </is>
-      </c>
-      <c r="B72" s="23" t="inlineStr">
-        <is>
-          <t>Proposed resolution</t>
-        </is>
-      </c>
-      <c r="C72" s="14" t="inlineStr">
-        <is>
-          <t>What the test team proposes to the FRS owner</t>
-        </is>
-      </c>
-      <c r="D72" s="14" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:D72"/>
+  <autoFilter ref="A4:D65"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -3006,7 +2574,7 @@
       <c r="E5" s="12" t="inlineStr"/>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Internal draft from FRS BRD-12 v1.0 and the Submitted Policies build design</t>
+          <t>Internal draft from FRS BRD-12 v1.0</t>
         </is>
       </c>
     </row>
@@ -5299,7 +4867,7 @@
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>Before the Renewal adapter exists, the hand-off shows as pending and no letter is sent.</t>
+          <t>While Renewal is not in use, the hand-off shows as pending and no letter is sent.</t>
         </is>
       </c>
       <c r="E72" s="12" t="inlineStr">
@@ -6545,7 +6113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R126"/>
+  <dimension ref="A1:Q126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6560,12 +6128,11 @@
     <col width="52" customWidth="1" min="10" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -6600,7 +6167,6 @@
       <c r="O3" s="25" t="n"/>
       <c r="P3" s="25" t="n"/>
       <c r="Q3" s="25" t="n"/>
-      <c r="R3" s="25" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
@@ -6665,32 +6231,27 @@
       </c>
       <c r="M4" s="26" t="inlineStr">
         <is>
-          <t>Automation reference</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="N4" s="26" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Actual result</t>
         </is>
       </c>
       <c r="O4" s="26" t="inlineStr">
         <is>
-          <t>Actual result</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="P4" s="26" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="Q4" s="26" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="R4" s="26" t="inlineStr">
-        <is>
-          <t>Defect ID</t>
+          <t>Issue ID</t>
         </is>
       </c>
     </row>
@@ -6756,16 +6317,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M5" s="12" t="inlineStr"/>
-      <c r="N5" s="27" t="inlineStr">
+      <c r="M5" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N5" s="12" t="n"/>
       <c r="O5" s="12" t="n"/>
-      <c r="P5" s="12" t="n"/>
-      <c r="Q5" s="28" t="n"/>
-      <c r="R5" s="12" t="n"/>
+      <c r="P5" s="28" t="n"/>
+      <c r="Q5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -6829,16 +6389,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="27" t="inlineStr">
+      <c r="M6" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N6" s="12" t="n"/>
       <c r="O6" s="12" t="n"/>
-      <c r="P6" s="12" t="n"/>
-      <c r="Q6" s="28" t="n"/>
-      <c r="R6" s="12" t="n"/>
+      <c r="P6" s="28" t="n"/>
+      <c r="Q6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -6901,16 +6460,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="27" t="inlineStr">
+      <c r="M7" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N7" s="12" t="n"/>
       <c r="O7" s="12" t="n"/>
-      <c r="P7" s="12" t="n"/>
-      <c r="Q7" s="28" t="n"/>
-      <c r="R7" s="12" t="n"/>
+      <c r="P7" s="28" t="n"/>
+      <c r="Q7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -6974,16 +6532,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M8" s="12" t="inlineStr"/>
-      <c r="N8" s="27" t="inlineStr">
+      <c r="M8" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N8" s="12" t="n"/>
       <c r="O8" s="12" t="n"/>
-      <c r="P8" s="12" t="n"/>
-      <c r="Q8" s="28" t="n"/>
-      <c r="R8" s="12" t="n"/>
+      <c r="P8" s="28" t="n"/>
+      <c r="Q8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -7047,16 +6604,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M9" s="12" t="inlineStr"/>
-      <c r="N9" s="27" t="inlineStr">
+      <c r="M9" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N9" s="12" t="n"/>
       <c r="O9" s="12" t="n"/>
-      <c r="P9" s="12" t="n"/>
-      <c r="Q9" s="28" t="n"/>
-      <c r="R9" s="12" t="n"/>
+      <c r="P9" s="28" t="n"/>
+      <c r="Q9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -7120,16 +6676,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M10" s="12" t="inlineStr"/>
-      <c r="N10" s="27" t="inlineStr">
+      <c r="M10" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N10" s="12" t="n"/>
       <c r="O10" s="12" t="n"/>
-      <c r="P10" s="12" t="n"/>
-      <c r="Q10" s="28" t="n"/>
-      <c r="R10" s="12" t="n"/>
+      <c r="P10" s="28" t="n"/>
+      <c r="Q10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -7192,16 +6747,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="27" t="inlineStr">
+      <c r="M11" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N11" s="12" t="n"/>
       <c r="O11" s="12" t="n"/>
-      <c r="P11" s="12" t="n"/>
-      <c r="Q11" s="28" t="n"/>
-      <c r="R11" s="12" t="n"/>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -7264,16 +6818,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M12" s="12" t="inlineStr"/>
-      <c r="N12" s="27" t="inlineStr">
+      <c r="M12" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N12" s="12" t="n"/>
       <c r="O12" s="12" t="n"/>
-      <c r="P12" s="12" t="n"/>
-      <c r="Q12" s="28" t="n"/>
-      <c r="R12" s="12" t="n"/>
+      <c r="P12" s="28" t="n"/>
+      <c r="Q12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -7336,16 +6889,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M13" s="12" t="inlineStr"/>
-      <c r="N13" s="27" t="inlineStr">
+      <c r="M13" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N13" s="12" t="n"/>
       <c r="O13" s="12" t="n"/>
-      <c r="P13" s="12" t="n"/>
-      <c r="Q13" s="28" t="n"/>
-      <c r="R13" s="12" t="n"/>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -7408,16 +6960,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M14" s="12" t="inlineStr"/>
-      <c r="N14" s="27" t="inlineStr">
+      <c r="M14" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N14" s="12" t="n"/>
       <c r="O14" s="12" t="n"/>
-      <c r="P14" s="12" t="n"/>
-      <c r="Q14" s="28" t="n"/>
-      <c r="R14" s="12" t="n"/>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -7481,16 +7032,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M15" s="12" t="inlineStr"/>
-      <c r="N15" s="27" t="inlineStr">
+      <c r="M15" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N15" s="12" t="n"/>
       <c r="O15" s="12" t="n"/>
-      <c r="P15" s="12" t="n"/>
-      <c r="Q15" s="28" t="n"/>
-      <c r="R15" s="12" t="n"/>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -7554,16 +7104,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M16" s="12" t="inlineStr"/>
-      <c r="N16" s="27" t="inlineStr">
+      <c r="M16" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N16" s="12" t="n"/>
       <c r="O16" s="12" t="n"/>
-      <c r="P16" s="12" t="n"/>
-      <c r="Q16" s="28" t="n"/>
-      <c r="R16" s="12" t="n"/>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -7626,16 +7175,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M17" s="12" t="inlineStr"/>
-      <c r="N17" s="27" t="inlineStr">
+      <c r="M17" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N17" s="12" t="n"/>
       <c r="O17" s="12" t="n"/>
-      <c r="P17" s="12" t="n"/>
-      <c r="Q17" s="28" t="n"/>
-      <c r="R17" s="12" t="n"/>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -7698,16 +7246,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M18" s="12" t="inlineStr"/>
-      <c r="N18" s="27" t="inlineStr">
+      <c r="M18" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N18" s="12" t="n"/>
       <c r="O18" s="12" t="n"/>
-      <c r="P18" s="12" t="n"/>
-      <c r="Q18" s="28" t="n"/>
-      <c r="R18" s="12" t="n"/>
+      <c r="P18" s="28" t="n"/>
+      <c r="Q18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -7771,16 +7318,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M19" s="12" t="inlineStr"/>
-      <c r="N19" s="27" t="inlineStr">
+      <c r="M19" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N19" s="12" t="n"/>
       <c r="O19" s="12" t="n"/>
-      <c r="P19" s="12" t="n"/>
-      <c r="Q19" s="28" t="n"/>
-      <c r="R19" s="12" t="n"/>
+      <c r="P19" s="28" t="n"/>
+      <c r="Q19" s="12" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -7843,16 +7389,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M20" s="12" t="inlineStr"/>
-      <c r="N20" s="27" t="inlineStr">
+      <c r="M20" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N20" s="12" t="n"/>
       <c r="O20" s="12" t="n"/>
-      <c r="P20" s="12" t="n"/>
-      <c r="Q20" s="28" t="n"/>
-      <c r="R20" s="12" t="n"/>
+      <c r="P20" s="28" t="n"/>
+      <c r="Q20" s="12" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -7916,16 +7461,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M21" s="12" t="inlineStr"/>
-      <c r="N21" s="27" t="inlineStr">
+      <c r="M21" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N21" s="12" t="n"/>
       <c r="O21" s="12" t="n"/>
-      <c r="P21" s="12" t="n"/>
-      <c r="Q21" s="28" t="n"/>
-      <c r="R21" s="12" t="n"/>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="12" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -7989,16 +7533,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M22" s="12" t="inlineStr"/>
-      <c r="N22" s="27" t="inlineStr">
+      <c r="M22" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N22" s="12" t="n"/>
       <c r="O22" s="12" t="n"/>
-      <c r="P22" s="12" t="n"/>
-      <c r="Q22" s="28" t="n"/>
-      <c r="R22" s="12" t="n"/>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="12" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -8062,16 +7605,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M23" s="12" t="inlineStr"/>
-      <c r="N23" s="27" t="inlineStr">
+      <c r="M23" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N23" s="12" t="n"/>
       <c r="O23" s="12" t="n"/>
-      <c r="P23" s="12" t="n"/>
-      <c r="Q23" s="28" t="n"/>
-      <c r="R23" s="12" t="n"/>
+      <c r="P23" s="28" t="n"/>
+      <c r="Q23" s="12" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
@@ -8134,16 +7676,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M24" s="12" t="inlineStr"/>
-      <c r="N24" s="27" t="inlineStr">
+      <c r="M24" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N24" s="12" t="n"/>
       <c r="O24" s="12" t="n"/>
-      <c r="P24" s="12" t="n"/>
-      <c r="Q24" s="28" t="n"/>
-      <c r="R24" s="12" t="n"/>
+      <c r="P24" s="28" t="n"/>
+      <c r="Q24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -8206,16 +7747,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M25" s="12" t="inlineStr"/>
-      <c r="N25" s="27" t="inlineStr">
+      <c r="M25" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N25" s="12" t="n"/>
       <c r="O25" s="12" t="n"/>
-      <c r="P25" s="12" t="n"/>
-      <c r="Q25" s="28" t="n"/>
-      <c r="R25" s="12" t="n"/>
+      <c r="P25" s="28" t="n"/>
+      <c r="Q25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
@@ -8279,16 +7819,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M26" s="12" t="inlineStr"/>
-      <c r="N26" s="27" t="inlineStr">
+      <c r="M26" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N26" s="12" t="n"/>
       <c r="O26" s="12" t="n"/>
-      <c r="P26" s="12" t="n"/>
-      <c r="Q26" s="28" t="n"/>
-      <c r="R26" s="12" t="n"/>
+      <c r="P26" s="28" t="n"/>
+      <c r="Q26" s="12" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -8352,16 +7891,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M27" s="12" t="inlineStr"/>
-      <c r="N27" s="27" t="inlineStr">
+      <c r="M27" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N27" s="12" t="n"/>
       <c r="O27" s="12" t="n"/>
-      <c r="P27" s="12" t="n"/>
-      <c r="Q27" s="28" t="n"/>
-      <c r="R27" s="12" t="n"/>
+      <c r="P27" s="28" t="n"/>
+      <c r="Q27" s="12" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
@@ -8424,16 +7962,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M28" s="12" t="inlineStr"/>
-      <c r="N28" s="27" t="inlineStr">
+      <c r="M28" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N28" s="12" t="n"/>
       <c r="O28" s="12" t="n"/>
-      <c r="P28" s="12" t="n"/>
-      <c r="Q28" s="28" t="n"/>
-      <c r="R28" s="12" t="n"/>
+      <c r="P28" s="28" t="n"/>
+      <c r="Q28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
@@ -8496,16 +8033,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M29" s="12" t="inlineStr"/>
-      <c r="N29" s="27" t="inlineStr">
+      <c r="M29" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N29" s="12" t="n"/>
       <c r="O29" s="12" t="n"/>
-      <c r="P29" s="12" t="n"/>
-      <c r="Q29" s="28" t="n"/>
-      <c r="R29" s="12" t="n"/>
+      <c r="P29" s="28" t="n"/>
+      <c r="Q29" s="12" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
@@ -8568,16 +8104,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M30" s="12" t="inlineStr"/>
-      <c r="N30" s="27" t="inlineStr">
+      <c r="M30" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N30" s="12" t="n"/>
       <c r="O30" s="12" t="n"/>
-      <c r="P30" s="12" t="n"/>
-      <c r="Q30" s="28" t="n"/>
-      <c r="R30" s="12" t="n"/>
+      <c r="P30" s="28" t="n"/>
+      <c r="Q30" s="12" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
@@ -8640,16 +8175,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M31" s="12" t="inlineStr"/>
-      <c r="N31" s="27" t="inlineStr">
+      <c r="M31" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N31" s="12" t="n"/>
       <c r="O31" s="12" t="n"/>
-      <c r="P31" s="12" t="n"/>
-      <c r="Q31" s="28" t="n"/>
-      <c r="R31" s="12" t="n"/>
+      <c r="P31" s="28" t="n"/>
+      <c r="Q31" s="12" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -8712,16 +8246,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M32" s="12" t="inlineStr"/>
-      <c r="N32" s="27" t="inlineStr">
+      <c r="M32" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N32" s="12" t="n"/>
       <c r="O32" s="12" t="n"/>
-      <c r="P32" s="12" t="n"/>
-      <c r="Q32" s="28" t="n"/>
-      <c r="R32" s="12" t="n"/>
+      <c r="P32" s="28" t="n"/>
+      <c r="Q32" s="12" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
@@ -8784,16 +8317,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M33" s="12" t="inlineStr"/>
-      <c r="N33" s="27" t="inlineStr">
+      <c r="M33" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N33" s="12" t="n"/>
       <c r="O33" s="12" t="n"/>
-      <c r="P33" s="12" t="n"/>
-      <c r="Q33" s="28" t="n"/>
-      <c r="R33" s="12" t="n"/>
+      <c r="P33" s="28" t="n"/>
+      <c r="Q33" s="12" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
@@ -8856,16 +8388,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M34" s="12" t="inlineStr"/>
-      <c r="N34" s="27" t="inlineStr">
+      <c r="M34" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N34" s="12" t="n"/>
       <c r="O34" s="12" t="n"/>
-      <c r="P34" s="12" t="n"/>
-      <c r="Q34" s="28" t="n"/>
-      <c r="R34" s="12" t="n"/>
+      <c r="P34" s="28" t="n"/>
+      <c r="Q34" s="12" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
@@ -8905,7 +8436,7 @@
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I35" s="12" t="inlineStr">
@@ -8915,12 +8446,12 @@
       </c>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>1. As polreview look for Export; call the export.</t>
+          <t>1. As polreview look for Export; send a direct export request.</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>No Export button; the call is refused.
+          <t>No Export button; a direct request is refused.
 Message "You are not permitted to perform this action".</t>
         </is>
       </c>
@@ -8929,16 +8460,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M35" s="12" t="inlineStr"/>
-      <c r="N35" s="27" t="inlineStr">
+      <c r="M35" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N35" s="12" t="n"/>
       <c r="O35" s="12" t="n"/>
-      <c r="P35" s="12" t="n"/>
-      <c r="Q35" s="28" t="n"/>
-      <c r="R35" s="12" t="n"/>
+      <c r="P35" s="28" t="n"/>
+      <c r="Q35" s="12" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
@@ -9001,16 +8531,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M36" s="12" t="inlineStr"/>
-      <c r="N36" s="27" t="inlineStr">
+      <c r="M36" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N36" s="12" t="n"/>
       <c r="O36" s="12" t="n"/>
-      <c r="P36" s="12" t="n"/>
-      <c r="Q36" s="28" t="n"/>
-      <c r="R36" s="12" t="n"/>
+      <c r="P36" s="28" t="n"/>
+      <c r="Q36" s="12" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
@@ -9073,16 +8602,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M37" s="12" t="inlineStr"/>
-      <c r="N37" s="27" t="inlineStr">
+      <c r="M37" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N37" s="12" t="n"/>
       <c r="O37" s="12" t="n"/>
-      <c r="P37" s="12" t="n"/>
-      <c r="Q37" s="28" t="n"/>
-      <c r="R37" s="12" t="n"/>
+      <c r="P37" s="28" t="n"/>
+      <c r="Q37" s="12" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
@@ -9145,16 +8673,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M38" s="12" t="inlineStr"/>
-      <c r="N38" s="27" t="inlineStr">
+      <c r="M38" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N38" s="12" t="n"/>
       <c r="O38" s="12" t="n"/>
-      <c r="P38" s="12" t="n"/>
-      <c r="Q38" s="28" t="n"/>
-      <c r="R38" s="12" t="n"/>
+      <c r="P38" s="28" t="n"/>
+      <c r="Q38" s="12" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
@@ -9194,7 +8721,7 @@
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I39" s="12" t="inlineStr">
@@ -9204,7 +8731,7 @@
       </c>
       <c r="J39" s="12" t="inlineStr">
         <is>
-          <t>1. Assign the disabled user as handler through the API.</t>
+          <t>1. Assign the disabled user as handler by a direct request.</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
@@ -9218,16 +8745,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M39" s="12" t="inlineStr"/>
-      <c r="N39" s="27" t="inlineStr">
+      <c r="M39" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N39" s="12" t="n"/>
       <c r="O39" s="12" t="n"/>
-      <c r="P39" s="12" t="n"/>
-      <c r="Q39" s="28" t="n"/>
-      <c r="R39" s="12" t="n"/>
+      <c r="P39" s="28" t="n"/>
+      <c r="Q39" s="12" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
@@ -9291,16 +8817,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M40" s="12" t="inlineStr"/>
-      <c r="N40" s="27" t="inlineStr">
+      <c r="M40" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N40" s="12" t="n"/>
       <c r="O40" s="12" t="n"/>
-      <c r="P40" s="12" t="n"/>
-      <c r="Q40" s="28" t="n"/>
-      <c r="R40" s="12" t="n"/>
+      <c r="P40" s="28" t="n"/>
+      <c r="Q40" s="12" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
@@ -9363,16 +8888,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M41" s="12" t="inlineStr"/>
-      <c r="N41" s="27" t="inlineStr">
+      <c r="M41" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N41" s="12" t="n"/>
       <c r="O41" s="12" t="n"/>
-      <c r="P41" s="12" t="n"/>
-      <c r="Q41" s="28" t="n"/>
-      <c r="R41" s="12" t="n"/>
+      <c r="P41" s="28" t="n"/>
+      <c r="Q41" s="12" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
@@ -9436,16 +8960,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M42" s="12" t="inlineStr"/>
-      <c r="N42" s="27" t="inlineStr">
+      <c r="M42" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N42" s="12" t="n"/>
       <c r="O42" s="12" t="n"/>
-      <c r="P42" s="12" t="n"/>
-      <c r="Q42" s="28" t="n"/>
-      <c r="R42" s="12" t="n"/>
+      <c r="P42" s="28" t="n"/>
+      <c r="Q42" s="12" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
@@ -9510,16 +9033,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M43" s="12" t="inlineStr"/>
-      <c r="N43" s="27" t="inlineStr">
+      <c r="M43" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N43" s="12" t="n"/>
       <c r="O43" s="12" t="n"/>
-      <c r="P43" s="12" t="n"/>
-      <c r="Q43" s="28" t="n"/>
-      <c r="R43" s="12" t="n"/>
+      <c r="P43" s="28" t="n"/>
+      <c r="Q43" s="12" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
@@ -9582,16 +9104,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M44" s="12" t="inlineStr"/>
-      <c r="N44" s="27" t="inlineStr">
+      <c r="M44" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N44" s="12" t="n"/>
       <c r="O44" s="12" t="n"/>
-      <c r="P44" s="12" t="n"/>
-      <c r="Q44" s="28" t="n"/>
-      <c r="R44" s="12" t="n"/>
+      <c r="P44" s="28" t="n"/>
+      <c r="Q44" s="12" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
@@ -9655,16 +9176,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M45" s="12" t="inlineStr"/>
-      <c r="N45" s="27" t="inlineStr">
+      <c r="M45" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N45" s="12" t="n"/>
       <c r="O45" s="12" t="n"/>
-      <c r="P45" s="12" t="n"/>
-      <c r="Q45" s="28" t="n"/>
-      <c r="R45" s="12" t="n"/>
+      <c r="P45" s="28" t="n"/>
+      <c r="Q45" s="12" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
@@ -9728,16 +9248,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M46" s="12" t="inlineStr"/>
-      <c r="N46" s="27" t="inlineStr">
+      <c r="M46" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N46" s="12" t="n"/>
       <c r="O46" s="12" t="n"/>
-      <c r="P46" s="12" t="n"/>
-      <c r="Q46" s="28" t="n"/>
-      <c r="R46" s="12" t="n"/>
+      <c r="P46" s="28" t="n"/>
+      <c r="Q46" s="12" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
@@ -9800,16 +9319,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M47" s="12" t="inlineStr"/>
-      <c r="N47" s="27" t="inlineStr">
+      <c r="M47" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N47" s="12" t="n"/>
       <c r="O47" s="12" t="n"/>
-      <c r="P47" s="12" t="n"/>
-      <c r="Q47" s="28" t="n"/>
-      <c r="R47" s="12" t="n"/>
+      <c r="P47" s="28" t="n"/>
+      <c r="Q47" s="12" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
@@ -9872,16 +9390,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M48" s="12" t="inlineStr"/>
-      <c r="N48" s="27" t="inlineStr">
+      <c r="M48" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N48" s="12" t="n"/>
       <c r="O48" s="12" t="n"/>
-      <c r="P48" s="12" t="n"/>
-      <c r="Q48" s="28" t="n"/>
-      <c r="R48" s="12" t="n"/>
+      <c r="P48" s="28" t="n"/>
+      <c r="Q48" s="12" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
@@ -9945,16 +9462,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M49" s="12" t="inlineStr"/>
-      <c r="N49" s="27" t="inlineStr">
+      <c r="M49" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N49" s="12" t="n"/>
       <c r="O49" s="12" t="n"/>
-      <c r="P49" s="12" t="n"/>
-      <c r="Q49" s="28" t="n"/>
-      <c r="R49" s="12" t="n"/>
+      <c r="P49" s="28" t="n"/>
+      <c r="Q49" s="12" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
@@ -10017,16 +9533,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M50" s="12" t="inlineStr"/>
-      <c r="N50" s="27" t="inlineStr">
+      <c r="M50" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N50" s="12" t="n"/>
       <c r="O50" s="12" t="n"/>
-      <c r="P50" s="12" t="n"/>
-      <c r="Q50" s="28" t="n"/>
-      <c r="R50" s="12" t="n"/>
+      <c r="P50" s="28" t="n"/>
+      <c r="Q50" s="12" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
@@ -10089,16 +9604,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M51" s="12" t="inlineStr"/>
-      <c r="N51" s="27" t="inlineStr">
+      <c r="M51" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N51" s="12" t="n"/>
       <c r="O51" s="12" t="n"/>
-      <c r="P51" s="12" t="n"/>
-      <c r="Q51" s="28" t="n"/>
-      <c r="R51" s="12" t="n"/>
+      <c r="P51" s="28" t="n"/>
+      <c r="Q51" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
@@ -10161,16 +9675,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M52" s="12" t="inlineStr"/>
-      <c r="N52" s="27" t="inlineStr">
+      <c r="M52" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N52" s="12" t="n"/>
       <c r="O52" s="12" t="n"/>
-      <c r="P52" s="12" t="n"/>
-      <c r="Q52" s="28" t="n"/>
-      <c r="R52" s="12" t="n"/>
+      <c r="P52" s="28" t="n"/>
+      <c r="Q52" s="12" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
@@ -10233,16 +9746,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M53" s="12" t="inlineStr"/>
-      <c r="N53" s="27" t="inlineStr">
+      <c r="M53" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N53" s="12" t="n"/>
       <c r="O53" s="12" t="n"/>
-      <c r="P53" s="12" t="n"/>
-      <c r="Q53" s="28" t="n"/>
-      <c r="R53" s="12" t="n"/>
+      <c r="P53" s="28" t="n"/>
+      <c r="Q53" s="12" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
@@ -10305,16 +9817,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M54" s="12" t="inlineStr"/>
-      <c r="N54" s="27" t="inlineStr">
+      <c r="M54" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N54" s="12" t="n"/>
       <c r="O54" s="12" t="n"/>
-      <c r="P54" s="12" t="n"/>
-      <c r="Q54" s="28" t="n"/>
-      <c r="R54" s="12" t="n"/>
+      <c r="P54" s="28" t="n"/>
+      <c r="Q54" s="12" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
@@ -10377,16 +9888,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M55" s="12" t="inlineStr"/>
-      <c r="N55" s="27" t="inlineStr">
+      <c r="M55" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N55" s="12" t="n"/>
       <c r="O55" s="12" t="n"/>
-      <c r="P55" s="12" t="n"/>
-      <c r="Q55" s="28" t="n"/>
-      <c r="R55" s="12" t="n"/>
+      <c r="P55" s="28" t="n"/>
+      <c r="Q55" s="12" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
@@ -10449,16 +9959,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M56" s="12" t="inlineStr"/>
-      <c r="N56" s="27" t="inlineStr">
+      <c r="M56" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N56" s="12" t="n"/>
       <c r="O56" s="12" t="n"/>
-      <c r="P56" s="12" t="n"/>
-      <c r="Q56" s="28" t="n"/>
-      <c r="R56" s="12" t="n"/>
+      <c r="P56" s="28" t="n"/>
+      <c r="Q56" s="12" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
@@ -10521,16 +10030,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M57" s="12" t="inlineStr"/>
-      <c r="N57" s="27" t="inlineStr">
+      <c r="M57" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N57" s="12" t="n"/>
       <c r="O57" s="12" t="n"/>
-      <c r="P57" s="12" t="n"/>
-      <c r="Q57" s="28" t="n"/>
-      <c r="R57" s="12" t="n"/>
+      <c r="P57" s="28" t="n"/>
+      <c r="Q57" s="12" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
@@ -10593,16 +10101,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M58" s="12" t="inlineStr"/>
-      <c r="N58" s="27" t="inlineStr">
+      <c r="M58" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N58" s="12" t="n"/>
       <c r="O58" s="12" t="n"/>
-      <c r="P58" s="12" t="n"/>
-      <c r="Q58" s="28" t="n"/>
-      <c r="R58" s="12" t="n"/>
+      <c r="P58" s="28" t="n"/>
+      <c r="Q58" s="12" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
@@ -10666,16 +10173,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M59" s="12" t="inlineStr"/>
-      <c r="N59" s="27" t="inlineStr">
+      <c r="M59" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N59" s="12" t="n"/>
       <c r="O59" s="12" t="n"/>
-      <c r="P59" s="12" t="n"/>
-      <c r="Q59" s="28" t="n"/>
-      <c r="R59" s="12" t="n"/>
+      <c r="P59" s="28" t="n"/>
+      <c r="Q59" s="12" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
@@ -10738,16 +10244,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M60" s="12" t="inlineStr"/>
-      <c r="N60" s="27" t="inlineStr">
+      <c r="M60" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N60" s="12" t="n"/>
       <c r="O60" s="12" t="n"/>
-      <c r="P60" s="12" t="n"/>
-      <c r="Q60" s="28" t="n"/>
-      <c r="R60" s="12" t="n"/>
+      <c r="P60" s="28" t="n"/>
+      <c r="Q60" s="12" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
@@ -10810,16 +10315,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M61" s="12" t="inlineStr"/>
-      <c r="N61" s="27" t="inlineStr">
+      <c r="M61" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N61" s="12" t="n"/>
       <c r="O61" s="12" t="n"/>
-      <c r="P61" s="12" t="n"/>
-      <c r="Q61" s="28" t="n"/>
-      <c r="R61" s="12" t="n"/>
+      <c r="P61" s="28" t="n"/>
+      <c r="Q61" s="12" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -10883,16 +10387,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M62" s="12" t="inlineStr"/>
-      <c r="N62" s="27" t="inlineStr">
+      <c r="M62" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N62" s="12" t="n"/>
       <c r="O62" s="12" t="n"/>
-      <c r="P62" s="12" t="n"/>
-      <c r="Q62" s="28" t="n"/>
-      <c r="R62" s="12" t="n"/>
+      <c r="P62" s="28" t="n"/>
+      <c r="Q62" s="12" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
@@ -10955,16 +10458,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M63" s="12" t="inlineStr"/>
-      <c r="N63" s="27" t="inlineStr">
+      <c r="M63" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N63" s="12" t="n"/>
       <c r="O63" s="12" t="n"/>
-      <c r="P63" s="12" t="n"/>
-      <c r="Q63" s="28" t="n"/>
-      <c r="R63" s="12" t="n"/>
+      <c r="P63" s="28" t="n"/>
+      <c r="Q63" s="12" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
@@ -11027,16 +10529,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M64" s="12" t="inlineStr"/>
-      <c r="N64" s="27" t="inlineStr">
+      <c r="M64" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N64" s="12" t="n"/>
       <c r="O64" s="12" t="n"/>
-      <c r="P64" s="12" t="n"/>
-      <c r="Q64" s="28" t="n"/>
-      <c r="R64" s="12" t="n"/>
+      <c r="P64" s="28" t="n"/>
+      <c r="Q64" s="12" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
@@ -11099,16 +10600,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M65" s="12" t="inlineStr"/>
-      <c r="N65" s="27" t="inlineStr">
+      <c r="M65" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N65" s="12" t="n"/>
       <c r="O65" s="12" t="n"/>
-      <c r="P65" s="12" t="n"/>
-      <c r="Q65" s="28" t="n"/>
-      <c r="R65" s="12" t="n"/>
+      <c r="P65" s="28" t="n"/>
+      <c r="Q65" s="12" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
@@ -11172,16 +10672,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M66" s="12" t="inlineStr"/>
-      <c r="N66" s="27" t="inlineStr">
+      <c r="M66" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N66" s="12" t="n"/>
       <c r="O66" s="12" t="n"/>
-      <c r="P66" s="12" t="n"/>
-      <c r="Q66" s="28" t="n"/>
-      <c r="R66" s="12" t="n"/>
+      <c r="P66" s="28" t="n"/>
+      <c r="Q66" s="12" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
@@ -11244,16 +10743,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M67" s="12" t="inlineStr"/>
-      <c r="N67" s="27" t="inlineStr">
+      <c r="M67" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N67" s="12" t="n"/>
       <c r="O67" s="12" t="n"/>
-      <c r="P67" s="12" t="n"/>
-      <c r="Q67" s="28" t="n"/>
-      <c r="R67" s="12" t="n"/>
+      <c r="P67" s="28" t="n"/>
+      <c r="Q67" s="12" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
@@ -11317,16 +10815,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M68" s="12" t="inlineStr"/>
-      <c r="N68" s="27" t="inlineStr">
+      <c r="M68" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N68" s="12" t="n"/>
       <c r="O68" s="12" t="n"/>
-      <c r="P68" s="12" t="n"/>
-      <c r="Q68" s="28" t="n"/>
-      <c r="R68" s="12" t="n"/>
+      <c r="P68" s="28" t="n"/>
+      <c r="Q68" s="12" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
@@ -11390,16 +10887,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M69" s="12" t="inlineStr"/>
-      <c r="N69" s="27" t="inlineStr">
+      <c r="M69" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N69" s="12" t="n"/>
       <c r="O69" s="12" t="n"/>
-      <c r="P69" s="12" t="n"/>
-      <c r="Q69" s="28" t="n"/>
-      <c r="R69" s="12" t="n"/>
+      <c r="P69" s="28" t="n"/>
+      <c r="Q69" s="12" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
@@ -11463,16 +10959,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M70" s="12" t="inlineStr"/>
-      <c r="N70" s="27" t="inlineStr">
+      <c r="M70" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N70" s="12" t="n"/>
       <c r="O70" s="12" t="n"/>
-      <c r="P70" s="12" t="n"/>
-      <c r="Q70" s="28" t="n"/>
-      <c r="R70" s="12" t="n"/>
+      <c r="P70" s="28" t="n"/>
+      <c r="Q70" s="12" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
@@ -11535,16 +11030,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M71" s="12" t="inlineStr"/>
-      <c r="N71" s="27" t="inlineStr">
+      <c r="M71" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N71" s="12" t="n"/>
       <c r="O71" s="12" t="n"/>
-      <c r="P71" s="12" t="n"/>
-      <c r="Q71" s="28" t="n"/>
-      <c r="R71" s="12" t="n"/>
+      <c r="P71" s="28" t="n"/>
+      <c r="Q71" s="12" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
@@ -11608,16 +11102,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M72" s="12" t="inlineStr"/>
-      <c r="N72" s="27" t="inlineStr">
+      <c r="M72" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N72" s="12" t="n"/>
       <c r="O72" s="12" t="n"/>
-      <c r="P72" s="12" t="n"/>
-      <c r="Q72" s="28" t="n"/>
-      <c r="R72" s="12" t="n"/>
+      <c r="P72" s="28" t="n"/>
+      <c r="Q72" s="12" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
@@ -11681,16 +11174,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M73" s="12" t="inlineStr"/>
-      <c r="N73" s="27" t="inlineStr">
+      <c r="M73" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N73" s="12" t="n"/>
       <c r="O73" s="12" t="n"/>
-      <c r="P73" s="12" t="n"/>
-      <c r="Q73" s="28" t="n"/>
-      <c r="R73" s="12" t="n"/>
+      <c r="P73" s="28" t="n"/>
+      <c r="Q73" s="12" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
@@ -11753,16 +11245,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M74" s="12" t="inlineStr"/>
-      <c r="N74" s="27" t="inlineStr">
+      <c r="M74" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N74" s="12" t="n"/>
       <c r="O74" s="12" t="n"/>
-      <c r="P74" s="12" t="n"/>
-      <c r="Q74" s="28" t="n"/>
-      <c r="R74" s="12" t="n"/>
+      <c r="P74" s="28" t="n"/>
+      <c r="Q74" s="12" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
@@ -11825,16 +11316,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M75" s="12" t="inlineStr"/>
-      <c r="N75" s="27" t="inlineStr">
+      <c r="M75" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N75" s="12" t="n"/>
       <c r="O75" s="12" t="n"/>
-      <c r="P75" s="12" t="n"/>
-      <c r="Q75" s="28" t="n"/>
-      <c r="R75" s="12" t="n"/>
+      <c r="P75" s="28" t="n"/>
+      <c r="Q75" s="12" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
@@ -11899,16 +11389,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M76" s="12" t="inlineStr"/>
-      <c r="N76" s="27" t="inlineStr">
+      <c r="M76" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N76" s="12" t="n"/>
       <c r="O76" s="12" t="n"/>
-      <c r="P76" s="12" t="n"/>
-      <c r="Q76" s="28" t="n"/>
-      <c r="R76" s="12" t="n"/>
+      <c r="P76" s="28" t="n"/>
+      <c r="Q76" s="12" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
@@ -11972,16 +11461,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M77" s="12" t="inlineStr"/>
-      <c r="N77" s="27" t="inlineStr">
+      <c r="M77" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N77" s="12" t="n"/>
       <c r="O77" s="12" t="n"/>
-      <c r="P77" s="12" t="n"/>
-      <c r="Q77" s="28" t="n"/>
-      <c r="R77" s="12" t="n"/>
+      <c r="P77" s="28" t="n"/>
+      <c r="Q77" s="12" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
@@ -12046,16 +11534,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M78" s="12" t="inlineStr"/>
-      <c r="N78" s="27" t="inlineStr">
+      <c r="M78" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N78" s="12" t="n"/>
       <c r="O78" s="12" t="n"/>
-      <c r="P78" s="12" t="n"/>
-      <c r="Q78" s="28" t="n"/>
-      <c r="R78" s="12" t="n"/>
+      <c r="P78" s="28" t="n"/>
+      <c r="Q78" s="12" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
@@ -12118,16 +11605,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M79" s="12" t="inlineStr"/>
-      <c r="N79" s="27" t="inlineStr">
+      <c r="M79" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N79" s="12" t="n"/>
       <c r="O79" s="12" t="n"/>
-      <c r="P79" s="12" t="n"/>
-      <c r="Q79" s="28" t="n"/>
-      <c r="R79" s="12" t="n"/>
+      <c r="P79" s="28" t="n"/>
+      <c r="Q79" s="12" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
@@ -12190,16 +11676,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M80" s="12" t="inlineStr"/>
-      <c r="N80" s="27" t="inlineStr">
+      <c r="M80" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N80" s="12" t="n"/>
       <c r="O80" s="12" t="n"/>
-      <c r="P80" s="12" t="n"/>
-      <c r="Q80" s="28" t="n"/>
-      <c r="R80" s="12" t="n"/>
+      <c r="P80" s="28" t="n"/>
+      <c r="Q80" s="12" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
@@ -12262,16 +11747,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M81" s="12" t="inlineStr"/>
-      <c r="N81" s="27" t="inlineStr">
+      <c r="M81" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N81" s="12" t="n"/>
       <c r="O81" s="12" t="n"/>
-      <c r="P81" s="12" t="n"/>
-      <c r="Q81" s="28" t="n"/>
-      <c r="R81" s="12" t="n"/>
+      <c r="P81" s="28" t="n"/>
+      <c r="Q81" s="12" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
@@ -12335,16 +11819,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M82" s="12" t="inlineStr"/>
-      <c r="N82" s="27" t="inlineStr">
+      <c r="M82" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N82" s="12" t="n"/>
       <c r="O82" s="12" t="n"/>
-      <c r="P82" s="12" t="n"/>
-      <c r="Q82" s="28" t="n"/>
-      <c r="R82" s="12" t="n"/>
+      <c r="P82" s="28" t="n"/>
+      <c r="Q82" s="12" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
@@ -12384,7 +11867,7 @@
       </c>
       <c r="H83" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I83" s="12" t="inlineStr">
@@ -12408,16 +11891,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M83" s="12" t="inlineStr"/>
-      <c r="N83" s="27" t="inlineStr">
+      <c r="M83" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N83" s="12" t="n"/>
       <c r="O83" s="12" t="n"/>
-      <c r="P83" s="12" t="n"/>
-      <c r="Q83" s="28" t="n"/>
-      <c r="R83" s="12" t="n"/>
+      <c r="P83" s="28" t="n"/>
+      <c r="Q83" s="12" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
@@ -12480,16 +11962,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M84" s="12" t="inlineStr"/>
-      <c r="N84" s="27" t="inlineStr">
+      <c r="M84" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N84" s="12" t="n"/>
       <c r="O84" s="12" t="n"/>
-      <c r="P84" s="12" t="n"/>
-      <c r="Q84" s="28" t="n"/>
-      <c r="R84" s="12" t="n"/>
+      <c r="P84" s="28" t="n"/>
+      <c r="Q84" s="12" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="12" t="inlineStr">
@@ -12554,16 +12035,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M85" s="12" t="inlineStr"/>
-      <c r="N85" s="27" t="inlineStr">
+      <c r="M85" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N85" s="12" t="n"/>
       <c r="O85" s="12" t="n"/>
-      <c r="P85" s="12" t="n"/>
-      <c r="Q85" s="28" t="n"/>
-      <c r="R85" s="12" t="n"/>
+      <c r="P85" s="28" t="n"/>
+      <c r="Q85" s="12" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="12" t="inlineStr">
@@ -12627,16 +12107,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M86" s="12" t="inlineStr"/>
-      <c r="N86" s="27" t="inlineStr">
+      <c r="M86" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N86" s="12" t="n"/>
       <c r="O86" s="12" t="n"/>
-      <c r="P86" s="12" t="n"/>
-      <c r="Q86" s="28" t="n"/>
-      <c r="R86" s="12" t="n"/>
+      <c r="P86" s="28" t="n"/>
+      <c r="Q86" s="12" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="12" t="inlineStr">
@@ -12699,16 +12178,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M87" s="12" t="inlineStr"/>
-      <c r="N87" s="27" t="inlineStr">
+      <c r="M87" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N87" s="12" t="n"/>
       <c r="O87" s="12" t="n"/>
-      <c r="P87" s="12" t="n"/>
-      <c r="Q87" s="28" t="n"/>
-      <c r="R87" s="12" t="n"/>
+      <c r="P87" s="28" t="n"/>
+      <c r="Q87" s="12" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="12" t="inlineStr">
@@ -12771,16 +12249,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M88" s="12" t="inlineStr"/>
-      <c r="N88" s="27" t="inlineStr">
+      <c r="M88" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N88" s="12" t="n"/>
       <c r="O88" s="12" t="n"/>
-      <c r="P88" s="12" t="n"/>
-      <c r="Q88" s="28" t="n"/>
-      <c r="R88" s="12" t="n"/>
+      <c r="P88" s="28" t="n"/>
+      <c r="Q88" s="12" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="12" t="inlineStr">
@@ -12825,7 +12302,7 @@
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SP-06 Rules and masters; TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SP-06 Rules and masters; TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J89" s="12" t="inlineStr">
@@ -12843,16 +12320,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M89" s="12" t="inlineStr"/>
-      <c r="N89" s="27" t="inlineStr">
+      <c r="M89" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N89" s="12" t="n"/>
       <c r="O89" s="12" t="n"/>
-      <c r="P89" s="12" t="n"/>
-      <c r="Q89" s="28" t="n"/>
-      <c r="R89" s="12" t="n"/>
+      <c r="P89" s="28" t="n"/>
+      <c r="Q89" s="12" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="12" t="inlineStr">
@@ -12897,7 +12373,7 @@
       </c>
       <c r="I90" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SP-06 Rules and masters; TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SP-06 Rules and masters; TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J90" s="12" t="inlineStr">
@@ -12915,16 +12391,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M90" s="12" t="inlineStr"/>
-      <c r="N90" s="27" t="inlineStr">
+      <c r="M90" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N90" s="12" t="n"/>
       <c r="O90" s="12" t="n"/>
-      <c r="P90" s="12" t="n"/>
-      <c r="Q90" s="28" t="n"/>
-      <c r="R90" s="12" t="n"/>
+      <c r="P90" s="28" t="n"/>
+      <c r="Q90" s="12" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="12" t="inlineStr">
@@ -12969,7 +12444,7 @@
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SP-06 Rules and masters; TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SP-06 Rules and masters; TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J91" s="12" t="inlineStr">
@@ -12987,16 +12462,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M91" s="12" t="inlineStr"/>
-      <c r="N91" s="27" t="inlineStr">
+      <c r="M91" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N91" s="12" t="n"/>
       <c r="O91" s="12" t="n"/>
-      <c r="P91" s="12" t="n"/>
-      <c r="Q91" s="28" t="n"/>
-      <c r="R91" s="12" t="n"/>
+      <c r="P91" s="28" t="n"/>
+      <c r="Q91" s="12" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="12" t="inlineStr">
@@ -13021,7 +12495,7 @@
       </c>
       <c r="E92" s="12" t="inlineStr">
         <is>
-          <t>Renewal adapter not deployed</t>
+          <t>Renewal not in use</t>
         </is>
       </c>
       <c r="F92" s="12" t="inlineStr">
@@ -13041,8 +12515,8 @@
       </c>
       <c r="I92" s="12" t="inlineStr">
         <is>
-          <t>Renewal module not deployed on the test environment.
-Data: TD-SP-06 Rules and masters; TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs as delivered</t>
+          <t>Renewal module not available on the test environment.
+Data: TD-SP-06 Rules and masters; TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J92" s="12" t="inlineStr">
@@ -13060,16 +12534,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M92" s="12" t="inlineStr"/>
-      <c r="N92" s="27" t="inlineStr">
+      <c r="M92" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N92" s="12" t="n"/>
       <c r="O92" s="12" t="n"/>
-      <c r="P92" s="12" t="n"/>
-      <c r="Q92" s="28" t="n"/>
-      <c r="R92" s="12" t="n"/>
+      <c r="P92" s="28" t="n"/>
+      <c r="Q92" s="12" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="12" t="inlineStr">
@@ -13114,7 +12587,7 @@
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SP-06 Rules and masters; TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SP-06 Rules and masters; TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J93" s="12" t="inlineStr">
@@ -13132,16 +12605,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M93" s="12" t="inlineStr"/>
-      <c r="N93" s="27" t="inlineStr">
+      <c r="M93" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N93" s="12" t="n"/>
       <c r="O93" s="12" t="n"/>
-      <c r="P93" s="12" t="n"/>
-      <c r="Q93" s="28" t="n"/>
-      <c r="R93" s="12" t="n"/>
+      <c r="P93" s="28" t="n"/>
+      <c r="Q93" s="12" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
@@ -13181,12 +12653,12 @@
       </c>
       <c r="H94" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I94" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SP-06 Rules and masters; TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SP-06 Rules and masters; TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J94" s="12" t="inlineStr">
@@ -13205,16 +12677,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M94" s="12" t="inlineStr"/>
-      <c r="N94" s="27" t="inlineStr">
+      <c r="M94" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N94" s="12" t="n"/>
       <c r="O94" s="12" t="n"/>
-      <c r="P94" s="12" t="n"/>
-      <c r="Q94" s="28" t="n"/>
-      <c r="R94" s="12" t="n"/>
+      <c r="P94" s="28" t="n"/>
+      <c r="Q94" s="12" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="12" t="inlineStr">
@@ -13259,7 +12730,7 @@
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SP-06 Rules and masters; TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SP-06 Rules and masters; TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J95" s="12" t="inlineStr">
@@ -13277,16 +12748,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M95" s="12" t="inlineStr"/>
-      <c r="N95" s="27" t="inlineStr">
+      <c r="M95" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N95" s="12" t="n"/>
       <c r="O95" s="12" t="n"/>
-      <c r="P95" s="12" t="n"/>
-      <c r="Q95" s="28" t="n"/>
-      <c r="R95" s="12" t="n"/>
+      <c r="P95" s="28" t="n"/>
+      <c r="Q95" s="12" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="12" t="inlineStr">
@@ -13349,16 +12819,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M96" s="12" t="inlineStr"/>
-      <c r="N96" s="27" t="inlineStr">
+      <c r="M96" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N96" s="12" t="n"/>
       <c r="O96" s="12" t="n"/>
-      <c r="P96" s="12" t="n"/>
-      <c r="Q96" s="28" t="n"/>
-      <c r="R96" s="12" t="n"/>
+      <c r="P96" s="28" t="n"/>
+      <c r="Q96" s="12" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="12" t="inlineStr">
@@ -13421,16 +12890,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M97" s="12" t="inlineStr"/>
-      <c r="N97" s="27" t="inlineStr">
+      <c r="M97" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N97" s="12" t="n"/>
       <c r="O97" s="12" t="n"/>
-      <c r="P97" s="12" t="n"/>
-      <c r="Q97" s="28" t="n"/>
-      <c r="R97" s="12" t="n"/>
+      <c r="P97" s="28" t="n"/>
+      <c r="Q97" s="12" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="12" t="inlineStr">
@@ -13493,16 +12961,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M98" s="12" t="inlineStr"/>
-      <c r="N98" s="27" t="inlineStr">
+      <c r="M98" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N98" s="12" t="n"/>
       <c r="O98" s="12" t="n"/>
-      <c r="P98" s="12" t="n"/>
-      <c r="Q98" s="28" t="n"/>
-      <c r="R98" s="12" t="n"/>
+      <c r="P98" s="28" t="n"/>
+      <c r="Q98" s="12" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="12" t="inlineStr">
@@ -13565,16 +13032,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M99" s="12" t="inlineStr"/>
-      <c r="N99" s="27" t="inlineStr">
+      <c r="M99" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N99" s="12" t="n"/>
       <c r="O99" s="12" t="n"/>
-      <c r="P99" s="12" t="n"/>
-      <c r="Q99" s="28" t="n"/>
-      <c r="R99" s="12" t="n"/>
+      <c r="P99" s="28" t="n"/>
+      <c r="Q99" s="12" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="12" t="inlineStr">
@@ -13637,16 +13103,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M100" s="12" t="inlineStr"/>
-      <c r="N100" s="27" t="inlineStr">
+      <c r="M100" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N100" s="12" t="n"/>
       <c r="O100" s="12" t="n"/>
-      <c r="P100" s="12" t="n"/>
-      <c r="Q100" s="28" t="n"/>
-      <c r="R100" s="12" t="n"/>
+      <c r="P100" s="28" t="n"/>
+      <c r="Q100" s="12" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="12" t="inlineStr">
@@ -13709,16 +13174,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M101" s="12" t="inlineStr"/>
-      <c r="N101" s="27" t="inlineStr">
+      <c r="M101" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N101" s="12" t="n"/>
       <c r="O101" s="12" t="n"/>
-      <c r="P101" s="12" t="n"/>
-      <c r="Q101" s="28" t="n"/>
-      <c r="R101" s="12" t="n"/>
+      <c r="P101" s="28" t="n"/>
+      <c r="Q101" s="12" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="12" t="inlineStr">
@@ -13782,16 +13246,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M102" s="12" t="inlineStr"/>
-      <c r="N102" s="27" t="inlineStr">
+      <c r="M102" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N102" s="12" t="n"/>
       <c r="O102" s="12" t="n"/>
-      <c r="P102" s="12" t="n"/>
-      <c r="Q102" s="28" t="n"/>
-      <c r="R102" s="12" t="n"/>
+      <c r="P102" s="28" t="n"/>
+      <c r="Q102" s="12" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="12" t="inlineStr">
@@ -13855,16 +13318,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M103" s="12" t="inlineStr"/>
-      <c r="N103" s="27" t="inlineStr">
+      <c r="M103" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N103" s="12" t="n"/>
       <c r="O103" s="12" t="n"/>
-      <c r="P103" s="12" t="n"/>
-      <c r="Q103" s="28" t="n"/>
-      <c r="R103" s="12" t="n"/>
+      <c r="P103" s="28" t="n"/>
+      <c r="Q103" s="12" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="12" t="inlineStr">
@@ -13909,7 +13371,7 @@
       </c>
       <c r="I104" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J104" s="12" t="inlineStr">
@@ -13927,16 +13389,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M104" s="12" t="inlineStr"/>
-      <c r="N104" s="27" t="inlineStr">
+      <c r="M104" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N104" s="12" t="n"/>
       <c r="O104" s="12" t="n"/>
-      <c r="P104" s="12" t="n"/>
-      <c r="Q104" s="28" t="n"/>
-      <c r="R104" s="12" t="n"/>
+      <c r="P104" s="28" t="n"/>
+      <c r="Q104" s="12" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="12" t="inlineStr">
@@ -13981,7 +13442,7 @@
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J105" s="12" t="inlineStr">
@@ -13999,16 +13460,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M105" s="12" t="inlineStr"/>
-      <c r="N105" s="27" t="inlineStr">
+      <c r="M105" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N105" s="12" t="n"/>
       <c r="O105" s="12" t="n"/>
-      <c r="P105" s="12" t="n"/>
-      <c r="Q105" s="28" t="n"/>
-      <c r="R105" s="12" t="n"/>
+      <c r="P105" s="28" t="n"/>
+      <c r="Q105" s="12" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="12" t="inlineStr">
@@ -14053,7 +13513,7 @@
       </c>
       <c r="I106" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J106" s="12" t="inlineStr">
@@ -14071,16 +13531,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M106" s="12" t="inlineStr"/>
-      <c r="N106" s="27" t="inlineStr">
+      <c r="M106" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N106" s="12" t="n"/>
       <c r="O106" s="12" t="n"/>
-      <c r="P106" s="12" t="n"/>
-      <c r="Q106" s="28" t="n"/>
-      <c r="R106" s="12" t="n"/>
+      <c r="P106" s="28" t="n"/>
+      <c r="Q106" s="12" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="12" t="inlineStr">
@@ -14125,7 +13584,7 @@
       </c>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J107" s="12" t="inlineStr">
@@ -14144,16 +13603,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M107" s="12" t="inlineStr"/>
-      <c r="N107" s="27" t="inlineStr">
+      <c r="M107" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N107" s="12" t="n"/>
       <c r="O107" s="12" t="n"/>
-      <c r="P107" s="12" t="n"/>
-      <c r="Q107" s="28" t="n"/>
-      <c r="R107" s="12" t="n"/>
+      <c r="P107" s="28" t="n"/>
+      <c r="Q107" s="12" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="12" t="inlineStr">
@@ -14198,7 +13656,7 @@
       </c>
       <c r="I108" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J108" s="12" t="inlineStr">
@@ -14217,16 +13675,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M108" s="12" t="inlineStr"/>
-      <c r="N108" s="27" t="inlineStr">
+      <c r="M108" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N108" s="12" t="n"/>
       <c r="O108" s="12" t="n"/>
-      <c r="P108" s="12" t="n"/>
-      <c r="Q108" s="28" t="n"/>
-      <c r="R108" s="12" t="n"/>
+      <c r="P108" s="28" t="n"/>
+      <c r="Q108" s="12" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="12" t="inlineStr">
@@ -14289,16 +13746,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M109" s="12" t="inlineStr"/>
-      <c r="N109" s="27" t="inlineStr">
+      <c r="M109" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N109" s="12" t="n"/>
       <c r="O109" s="12" t="n"/>
-      <c r="P109" s="12" t="n"/>
-      <c r="Q109" s="28" t="n"/>
-      <c r="R109" s="12" t="n"/>
+      <c r="P109" s="28" t="n"/>
+      <c r="Q109" s="12" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="12" t="inlineStr">
@@ -14361,16 +13817,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M110" s="12" t="inlineStr"/>
-      <c r="N110" s="27" t="inlineStr">
+      <c r="M110" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N110" s="12" t="n"/>
       <c r="O110" s="12" t="n"/>
-      <c r="P110" s="12" t="n"/>
-      <c r="Q110" s="28" t="n"/>
-      <c r="R110" s="12" t="n"/>
+      <c r="P110" s="28" t="n"/>
+      <c r="Q110" s="12" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="12" t="inlineStr">
@@ -14433,16 +13888,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M111" s="12" t="inlineStr"/>
-      <c r="N111" s="27" t="inlineStr">
+      <c r="M111" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N111" s="12" t="n"/>
       <c r="O111" s="12" t="n"/>
-      <c r="P111" s="12" t="n"/>
-      <c r="Q111" s="28" t="n"/>
-      <c r="R111" s="12" t="n"/>
+      <c r="P111" s="28" t="n"/>
+      <c r="Q111" s="12" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="12" t="inlineStr">
@@ -14505,16 +13959,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M112" s="12" t="inlineStr"/>
-      <c r="N112" s="27" t="inlineStr">
+      <c r="M112" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N112" s="12" t="n"/>
       <c r="O112" s="12" t="n"/>
-      <c r="P112" s="12" t="n"/>
-      <c r="Q112" s="28" t="n"/>
-      <c r="R112" s="12" t="n"/>
+      <c r="P112" s="28" t="n"/>
+      <c r="Q112" s="12" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="12" t="inlineStr">
@@ -14577,16 +14030,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M113" s="12" t="inlineStr"/>
-      <c r="N113" s="27" t="inlineStr">
+      <c r="M113" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N113" s="12" t="n"/>
       <c r="O113" s="12" t="n"/>
-      <c r="P113" s="12" t="n"/>
-      <c r="Q113" s="28" t="n"/>
-      <c r="R113" s="12" t="n"/>
+      <c r="P113" s="28" t="n"/>
+      <c r="Q113" s="12" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="12" t="inlineStr">
@@ -14649,16 +14101,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M114" s="12" t="inlineStr"/>
-      <c r="N114" s="27" t="inlineStr">
+      <c r="M114" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N114" s="12" t="n"/>
       <c r="O114" s="12" t="n"/>
-      <c r="P114" s="12" t="n"/>
-      <c r="Q114" s="28" t="n"/>
-      <c r="R114" s="12" t="n"/>
+      <c r="P114" s="28" t="n"/>
+      <c r="Q114" s="12" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="12" t="inlineStr">
@@ -14721,16 +14172,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M115" s="12" t="inlineStr"/>
-      <c r="N115" s="27" t="inlineStr">
+      <c r="M115" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N115" s="12" t="n"/>
       <c r="O115" s="12" t="n"/>
-      <c r="P115" s="12" t="n"/>
-      <c r="Q115" s="28" t="n"/>
-      <c r="R115" s="12" t="n"/>
+      <c r="P115" s="28" t="n"/>
+      <c r="Q115" s="12" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="12" t="inlineStr">
@@ -14770,7 +14220,7 @@
       </c>
       <c r="H116" s="12" t="inlineStr">
         <is>
-          <t>API call with the user's token (tester tool, for example Postman)</t>
+          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I116" s="12" t="inlineStr">
@@ -14794,16 +14244,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M116" s="12" t="inlineStr"/>
-      <c r="N116" s="27" t="inlineStr">
+      <c r="M116" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N116" s="12" t="n"/>
       <c r="O116" s="12" t="n"/>
-      <c r="P116" s="12" t="n"/>
-      <c r="Q116" s="28" t="n"/>
-      <c r="R116" s="12" t="n"/>
+      <c r="P116" s="28" t="n"/>
+      <c r="Q116" s="12" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="12" t="inlineStr">
@@ -14866,16 +14315,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M117" s="12" t="inlineStr"/>
-      <c r="N117" s="27" t="inlineStr">
+      <c r="M117" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N117" s="12" t="n"/>
       <c r="O117" s="12" t="n"/>
-      <c r="P117" s="12" t="n"/>
-      <c r="Q117" s="28" t="n"/>
-      <c r="R117" s="12" t="n"/>
+      <c r="P117" s="28" t="n"/>
+      <c r="Q117" s="12" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="12" t="inlineStr">
@@ -14938,16 +14386,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M118" s="12" t="inlineStr"/>
-      <c r="N118" s="27" t="inlineStr">
+      <c r="M118" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N118" s="12" t="n"/>
       <c r="O118" s="12" t="n"/>
-      <c r="P118" s="12" t="n"/>
-      <c r="Q118" s="28" t="n"/>
-      <c r="R118" s="12" t="n"/>
+      <c r="P118" s="28" t="n"/>
+      <c r="Q118" s="12" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="12" t="inlineStr">
@@ -15011,16 +14458,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M119" s="12" t="inlineStr"/>
-      <c r="N119" s="27" t="inlineStr">
+      <c r="M119" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N119" s="12" t="n"/>
       <c r="O119" s="12" t="n"/>
-      <c r="P119" s="12" t="n"/>
-      <c r="Q119" s="28" t="n"/>
-      <c r="R119" s="12" t="n"/>
+      <c r="P119" s="28" t="n"/>
+      <c r="Q119" s="12" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="12" t="inlineStr">
@@ -15083,16 +14529,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M120" s="12" t="inlineStr"/>
-      <c r="N120" s="27" t="inlineStr">
+      <c r="M120" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N120" s="12" t="n"/>
       <c r="O120" s="12" t="n"/>
-      <c r="P120" s="12" t="n"/>
-      <c r="Q120" s="28" t="n"/>
-      <c r="R120" s="12" t="n"/>
+      <c r="P120" s="28" t="n"/>
+      <c r="Q120" s="12" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="12" t="inlineStr">
@@ -15155,16 +14600,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M121" s="12" t="inlineStr"/>
-      <c r="N121" s="27" t="inlineStr">
+      <c r="M121" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N121" s="12" t="n"/>
       <c r="O121" s="12" t="n"/>
-      <c r="P121" s="12" t="n"/>
-      <c r="Q121" s="28" t="n"/>
-      <c r="R121" s="12" t="n"/>
+      <c r="P121" s="28" t="n"/>
+      <c r="Q121" s="12" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="12" t="inlineStr">
@@ -15214,12 +14658,12 @@
       </c>
       <c r="J122" s="12" t="inlineStr">
         <is>
-          <t>1. As sbmchecker run the report; call the export.</t>
+          <t>1. As sbmchecker run the report; send a direct export request.</t>
         </is>
       </c>
       <c r="K122" s="12" t="inlineStr">
         <is>
-          <t>No Export; the call is refused.
+          <t>No Export; a direct request is refused.
 Message "You are not permitted to perform this action".</t>
         </is>
       </c>
@@ -15228,16 +14672,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M122" s="12" t="inlineStr"/>
-      <c r="N122" s="27" t="inlineStr">
+      <c r="M122" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N122" s="12" t="n"/>
       <c r="O122" s="12" t="n"/>
-      <c r="P122" s="12" t="n"/>
-      <c r="Q122" s="28" t="n"/>
-      <c r="R122" s="12" t="n"/>
+      <c r="P122" s="28" t="n"/>
+      <c r="Q122" s="12" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="12" t="inlineStr">
@@ -15282,7 +14725,7 @@
       </c>
       <c r="I123" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SP-08 Review, TOR and handling-fee data; TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SP-08 Review, TOR and handling-fee data; TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J123" s="12" t="inlineStr">
@@ -15300,16 +14743,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M123" s="12" t="inlineStr"/>
-      <c r="N123" s="27" t="inlineStr">
+      <c r="M123" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N123" s="12" t="n"/>
       <c r="O123" s="12" t="n"/>
-      <c r="P123" s="12" t="n"/>
-      <c r="Q123" s="28" t="n"/>
-      <c r="R123" s="12" t="n"/>
+      <c r="P123" s="28" t="n"/>
+      <c r="Q123" s="12" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="12" t="inlineStr">
@@ -15354,7 +14796,7 @@
       </c>
       <c r="I124" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SP-08 Review, TOR and handling-fee data; TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SP-08 Review, TOR and handling-fee data; TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J124" s="12" t="inlineStr">
@@ -15372,16 +14814,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M124" s="12" t="inlineStr"/>
-      <c r="N124" s="27" t="inlineStr">
+      <c r="M124" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N124" s="12" t="n"/>
       <c r="O124" s="12" t="n"/>
-      <c r="P124" s="12" t="n"/>
-      <c r="Q124" s="28" t="n"/>
-      <c r="R124" s="12" t="n"/>
+      <c r="P124" s="28" t="n"/>
+      <c r="Q124" s="12" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="12" t="inlineStr">
@@ -15426,7 +14867,7 @@
       </c>
       <c r="I125" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SP-08 Review, TOR and handling-fee data; TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SP-08 Review, TOR and handling-fee data; TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J125" s="12" t="inlineStr">
@@ -15444,16 +14885,15 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M125" s="12" t="inlineStr"/>
-      <c r="N125" s="27" t="inlineStr">
+      <c r="M125" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N125" s="12" t="n"/>
       <c r="O125" s="12" t="n"/>
-      <c r="P125" s="12" t="n"/>
-      <c r="Q125" s="28" t="n"/>
-      <c r="R125" s="12" t="n"/>
+      <c r="P125" s="28" t="n"/>
+      <c r="Q125" s="12" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="12" t="inlineStr">
@@ -15498,7 +14938,7 @@
       </c>
       <c r="I126" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-SP-08 Review, TOR and handling-fee data; TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs as delivered</t>
+          <t>Data: TD-SP-08 Review, TOR and handling-fee data; TD-SP-09 Renewal candidates; TD-SP-10 Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="J126" s="12" t="inlineStr">
@@ -15516,23 +14956,22 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M126" s="12" t="inlineStr"/>
-      <c r="N126" s="27" t="inlineStr">
+      <c r="M126" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="N126" s="12" t="n"/>
       <c r="O126" s="12" t="n"/>
-      <c r="P126" s="12" t="n"/>
-      <c r="Q126" s="28" t="n"/>
-      <c r="R126" s="12" t="n"/>
+      <c r="P126" s="28" t="n"/>
+      <c r="Q126" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R126"/>
+  <autoFilter ref="A4:Q126"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A2:Q2"/>
   </mergeCells>
-  <conditionalFormatting sqref="N5:N626">
+  <conditionalFormatting sqref="M5:M626">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"Pass"</formula>
     </cfRule>
@@ -15546,19 +14985,19 @@
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:R626">
+  <conditionalFormatting sqref="A5:Q626">
     <cfRule type="expression" priority="5" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation sqref="F5:F626" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Type" error="Choose a value from the list (Type)." type="list">
-      <formula1>'_lists'!$B$1:$B$7</formula1>
+      <formula1>'_lists'!$B$1:$B$9</formula1>
     </dataValidation>
     <dataValidation sqref="L5:L626" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
       <formula1>'_lists'!$C$1:$C$3</formula1>
     </dataValidation>
-    <dataValidation sqref="N5:N626" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
+    <dataValidation sqref="M5:M626" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
       <formula1>'_lists'!$D$1:$D$5</formula1>
     </dataValidation>
   </dataValidations>
@@ -15582,7 +15021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15594,7 +15033,6 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -15621,7 +15059,6 @@
       <c r="G3" s="25" t="n"/>
       <c r="H3" s="25" t="n"/>
       <c r="I3" s="25" t="n"/>
-      <c r="J3" s="25" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
@@ -15666,11 +15103,6 @@
       </c>
       <c r="I4" s="26" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="J4" s="26" t="inlineStr">
-        <is>
           <t>Coverage</t>
         </is>
       </c>
@@ -15708,10 +15140,7 @@
       <c r="H5" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="27" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15750,10 +15179,7 @@
       <c r="H6" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="27" t="inlineStr">
+      <c r="I6" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15792,10 +15218,7 @@
       <c r="H7" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="27" t="inlineStr">
+      <c r="I7" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15834,10 +15257,7 @@
       <c r="H8" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="27" t="inlineStr">
+      <c r="I8" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15876,10 +15296,7 @@
       <c r="H9" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="27" t="inlineStr">
+      <c r="I9" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15918,10 +15335,7 @@
       <c r="H10" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="27" t="inlineStr">
+      <c r="I10" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -15960,10 +15374,7 @@
       <c r="H11" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="27" t="inlineStr">
+      <c r="I11" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16002,10 +15413,7 @@
       <c r="H12" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="27" t="inlineStr">
+      <c r="I12" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16044,10 +15452,7 @@
       <c r="H13" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="27" t="inlineStr">
+      <c r="I13" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16086,10 +15491,7 @@
       <c r="H14" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="27" t="inlineStr">
+      <c r="I14" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16128,10 +15530,7 @@
       <c r="H15" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="27" t="inlineStr">
+      <c r="I15" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16170,10 +15569,7 @@
       <c r="H16" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="27" t="inlineStr">
+      <c r="I16" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16212,10 +15608,7 @@
       <c r="H17" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="27" t="inlineStr">
+      <c r="I17" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16254,10 +15647,7 @@
       <c r="H18" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="27" t="inlineStr">
+      <c r="I18" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16296,10 +15686,7 @@
       <c r="H19" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="27" t="inlineStr">
+      <c r="I19" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16338,10 +15725,7 @@
       <c r="H20" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="27" t="inlineStr">
+      <c r="I20" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16380,10 +15764,7 @@
       <c r="H21" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="27" t="inlineStr">
+      <c r="I21" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16422,10 +15803,7 @@
       <c r="H22" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="27" t="inlineStr">
+      <c r="I22" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16464,10 +15842,7 @@
       <c r="H23" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="27" t="inlineStr">
+      <c r="I23" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16506,10 +15881,7 @@
       <c r="H24" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="27" t="inlineStr">
+      <c r="I24" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16548,10 +15920,7 @@
       <c r="H25" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="27" t="inlineStr">
+      <c r="I25" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16590,10 +15959,7 @@
       <c r="H26" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="27" t="inlineStr">
+      <c r="I26" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16632,10 +15998,7 @@
       <c r="H27" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="27" t="inlineStr">
+      <c r="I27" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16674,10 +16037,7 @@
       <c r="H28" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I28" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="27" t="inlineStr">
+      <c r="I28" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16716,10 +16076,7 @@
       <c r="H29" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="27" t="inlineStr">
+      <c r="I29" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16758,10 +16115,7 @@
       <c r="H30" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="27" t="inlineStr">
+      <c r="I30" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16800,10 +16154,7 @@
       <c r="H31" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="27" t="inlineStr">
+      <c r="I31" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16842,10 +16193,7 @@
       <c r="H32" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="27" t="inlineStr">
+      <c r="I32" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16884,10 +16232,7 @@
       <c r="H33" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="27" t="inlineStr">
+      <c r="I33" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16926,10 +16271,7 @@
       <c r="H34" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="27" t="inlineStr">
+      <c r="I34" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -16968,10 +16310,7 @@
       <c r="H35" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="27" t="inlineStr">
+      <c r="I35" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -17006,10 +16345,7 @@
       <c r="H36" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="27" t="inlineStr">
+      <c r="I36" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -17044,10 +16380,7 @@
       <c r="H37" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="27" t="inlineStr">
+      <c r="I37" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -17082,10 +16415,7 @@
       <c r="H38" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="27" t="inlineStr">
+      <c r="I38" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -17120,10 +16450,7 @@
       <c r="H39" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I39" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="27" t="inlineStr">
+      <c r="I39" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -17158,10 +16485,7 @@
       <c r="H40" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="27" t="inlineStr">
+      <c r="I40" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -17196,10 +16520,7 @@
       <c r="H41" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="27" t="inlineStr">
+      <c r="I41" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -17234,10 +16555,7 @@
       <c r="H42" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="27" t="inlineStr">
+      <c r="I42" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -17272,10 +16590,7 @@
       <c r="H43" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="27" t="inlineStr">
+      <c r="I43" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -17310,10 +16625,7 @@
       <c r="H44" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="27" t="inlineStr">
+      <c r="I44" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -17348,10 +16660,7 @@
       <c r="H45" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="27" t="inlineStr">
+      <c r="I45" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -17386,10 +16695,7 @@
       <c r="H46" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I46" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="27" t="inlineStr">
+      <c r="I46" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -17424,10 +16730,7 @@
       <c r="H47" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I47" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="27" t="inlineStr">
+      <c r="I47" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -17462,10 +16765,7 @@
       <c r="H48" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="27" t="inlineStr">
+      <c r="I48" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -17500,10 +16800,7 @@
       <c r="H49" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="27" t="inlineStr">
+      <c r="I49" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -17538,10 +16835,7 @@
       <c r="H50" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="27" t="inlineStr">
+      <c r="I50" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -17576,10 +16870,7 @@
       <c r="H51" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="27" t="inlineStr">
+      <c r="I51" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -17614,10 +16905,7 @@
       <c r="H52" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I52" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="27" t="inlineStr">
+      <c r="I52" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -17652,10 +16940,7 @@
       <c r="H53" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="27" t="inlineStr">
+      <c r="I53" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -17690,10 +16975,7 @@
       <c r="H54" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="27" t="inlineStr">
+      <c r="I54" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -17728,10 +17010,7 @@
       <c r="H55" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="27" t="inlineStr">
+      <c r="I55" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -17766,10 +17045,7 @@
       <c r="H56" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="27" t="inlineStr">
+      <c r="I56" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -17804,10 +17080,7 @@
       <c r="H57" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="27" t="inlineStr">
+      <c r="I57" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -17842,10 +17115,7 @@
       <c r="H58" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="27" t="inlineStr">
+      <c r="I58" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -17880,10 +17150,7 @@
       <c r="H59" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="27" t="inlineStr">
+      <c r="I59" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -17918,10 +17185,7 @@
       <c r="H60" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="27" t="inlineStr">
+      <c r="I60" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -17956,10 +17220,7 @@
       <c r="H61" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="27" t="inlineStr">
+      <c r="I61" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -17994,10 +17255,7 @@
       <c r="H62" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I62" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="27" t="inlineStr">
+      <c r="I62" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -18032,10 +17290,7 @@
       <c r="H63" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I63" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="27" t="inlineStr">
+      <c r="I63" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -18070,10 +17325,7 @@
       <c r="H64" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I64" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="27" t="inlineStr">
+      <c r="I64" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -18108,10 +17360,7 @@
       <c r="H65" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I65" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="27" t="inlineStr">
+      <c r="I65" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -18146,10 +17395,7 @@
       <c r="H66" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I66" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="27" t="inlineStr">
+      <c r="I66" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -18184,10 +17430,7 @@
       <c r="H67" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I67" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="27" t="inlineStr">
+      <c r="I67" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
@@ -18222,32 +17465,29 @@
       <c r="H68" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I68" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="27" t="inlineStr">
+      <c r="I68" s="27" t="inlineStr">
         <is>
           <t>Covered</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J68"/>
+  <autoFilter ref="A4:I68"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="J5:J568">
+  <conditionalFormatting sqref="I5:I568">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="2" stopIfTrue="1">
       <formula>"GAP"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:J568">
+  <conditionalFormatting sqref="A5:I568">
     <cfRule type="expression" priority="2" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J5:J568" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Coverage" error="Choose a value from the list (Coverage)." type="list">
+    <dataValidation sqref="I5:I568" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Coverage" error="Choose a value from the list (Coverage)." type="list">
       <formula1>'_lists'!$E$1:$E$2</formula1>
     </dataValidation>
   </dataValidations>
@@ -18347,7 +17587,7 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Planned seed V1970 of the build design; firehandler and ao2 created by the test lead with their user scope</t>
+          <t>Seed data; firehandler and ao2 created by the test lead with their user scope</t>
         </is>
       </c>
       <c r="E5" s="12" t="n">
@@ -18447,7 +17687,7 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Planned seed V1971; masked rows added by the test lead</t>
+          <t>Seed data; masked rows added by the test lead</t>
         </is>
       </c>
       <c r="E9" s="12" t="n">
@@ -18472,7 +17712,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Planned seed V1970 of the build design</t>
+          <t>Seed data</t>
         </is>
       </c>
       <c r="E10" s="12" t="n">
@@ -18497,7 +17737,7 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Planned seed V1971 of the build design</t>
+          <t>Seed data</t>
         </is>
       </c>
       <c r="E11" s="12" t="n">
@@ -18522,7 +17762,7 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Planned seed V1972; payments keyed in Collections by the test lead</t>
+          <t>Seed data; payments keyed in Collections by the test lead</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
@@ -18547,7 +17787,7 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Planned seeds V1971-V1972; expiry dates set by the test lead</t>
+          <t>Seed data; expiry dates set by the test lead</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
@@ -18562,7 +17802,7 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>Parameters and jobs as delivered</t>
+          <t>Parameters and jobs at their defaults</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -18572,7 +17812,7 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Configuration delivered with the build (FRS section 9.1)</t>
+          <t>Configuration of the SIT environment (FRS section 9.1)</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
@@ -18609,7 +17849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:L81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -18619,12 +17859,11 @@
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -18654,7 +17893,6 @@
       <c r="J3" s="25" t="n"/>
       <c r="K3" s="25" t="n"/>
       <c r="L3" s="25" t="n"/>
-      <c r="M3" s="25" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
@@ -18694,32 +17932,27 @@
       </c>
       <c r="H4" s="26" t="inlineStr">
         <is>
-          <t>Automation reference</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="I4" s="26" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Actual result</t>
         </is>
       </c>
       <c r="J4" s="26" t="inlineStr">
         <is>
-          <t>Actual result</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="K4" s="26" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="L4" s="26" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="M4" s="26" t="inlineStr">
-        <is>
-          <t>Defect ID</t>
+          <t>Issue ID</t>
         </is>
       </c>
     </row>
@@ -18759,16 +17992,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr"/>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="H5" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="28" t="n"/>
-      <c r="M5" s="12" t="n"/>
+      <c r="K5" s="28" t="n"/>
+      <c r="L5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -18806,16 +18038,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr"/>
-      <c r="I6" s="27" t="inlineStr">
+      <c r="H6" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I6" s="12" t="n"/>
       <c r="J6" s="12" t="n"/>
-      <c r="K6" s="12" t="n"/>
-      <c r="L6" s="28" t="n"/>
-      <c r="M6" s="12" t="n"/>
+      <c r="K6" s="28" t="n"/>
+      <c r="L6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -18853,16 +18084,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H7" s="12" t="inlineStr"/>
-      <c r="I7" s="27" t="inlineStr">
+      <c r="H7" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I7" s="12" t="n"/>
       <c r="J7" s="12" t="n"/>
-      <c r="K7" s="12" t="n"/>
-      <c r="L7" s="28" t="n"/>
-      <c r="M7" s="12" t="n"/>
+      <c r="K7" s="28" t="n"/>
+      <c r="L7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -18900,16 +18130,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr"/>
-      <c r="I8" s="27" t="inlineStr">
+      <c r="H8" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I8" s="12" t="n"/>
       <c r="J8" s="12" t="n"/>
-      <c r="K8" s="12" t="n"/>
-      <c r="L8" s="28" t="n"/>
-      <c r="M8" s="12" t="n"/>
+      <c r="K8" s="28" t="n"/>
+      <c r="L8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -18947,16 +18176,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr"/>
-      <c r="I9" s="27" t="inlineStr">
+      <c r="H9" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I9" s="12" t="n"/>
       <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="28" t="n"/>
-      <c r="M9" s="12" t="n"/>
+      <c r="K9" s="28" t="n"/>
+      <c r="L9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -18994,16 +18222,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr"/>
-      <c r="I10" s="27" t="inlineStr">
+      <c r="H10" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I10" s="12" t="n"/>
       <c r="J10" s="12" t="n"/>
-      <c r="K10" s="12" t="n"/>
-      <c r="L10" s="28" t="n"/>
-      <c r="M10" s="12" t="n"/>
+      <c r="K10" s="28" t="n"/>
+      <c r="L10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -19041,16 +18268,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr"/>
-      <c r="I11" s="27" t="inlineStr">
+      <c r="H11" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I11" s="12" t="n"/>
       <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="28" t="n"/>
-      <c r="M11" s="12" t="n"/>
+      <c r="K11" s="28" t="n"/>
+      <c r="L11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -19088,16 +18314,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr"/>
-      <c r="I12" s="27" t="inlineStr">
+      <c r="H12" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I12" s="12" t="n"/>
       <c r="J12" s="12" t="n"/>
-      <c r="K12" s="12" t="n"/>
-      <c r="L12" s="28" t="n"/>
-      <c r="M12" s="12" t="n"/>
+      <c r="K12" s="28" t="n"/>
+      <c r="L12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -19135,16 +18360,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr"/>
-      <c r="I13" s="27" t="inlineStr">
+      <c r="H13" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I13" s="12" t="n"/>
       <c r="J13" s="12" t="n"/>
-      <c r="K13" s="12" t="n"/>
-      <c r="L13" s="28" t="n"/>
-      <c r="M13" s="12" t="n"/>
+      <c r="K13" s="28" t="n"/>
+      <c r="L13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -19179,19 +18403,18 @@
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>Submitted Policies is not in the menu; the list call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H14" s="12" t="inlineStr"/>
-      <c r="I14" s="27" t="inlineStr">
+          <t>Submitted Policies is not in the menu; a direct list request is refused.</t>
+        </is>
+      </c>
+      <c r="H14" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I14" s="12" t="n"/>
       <c r="J14" s="12" t="n"/>
-      <c r="K14" s="12" t="n"/>
-      <c r="L14" s="28" t="n"/>
-      <c r="M14" s="12" t="n"/>
+      <c r="K14" s="28" t="n"/>
+      <c r="L14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -19226,19 +18449,18 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>Submitted Policies is not in the menu; the list call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="inlineStr"/>
-      <c r="I15" s="27" t="inlineStr">
+          <t>Submitted Policies is not in the menu; a direct list request is refused.</t>
+        </is>
+      </c>
+      <c r="H15" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I15" s="12" t="n"/>
       <c r="J15" s="12" t="n"/>
-      <c r="K15" s="12" t="n"/>
-      <c r="L15" s="28" t="n"/>
-      <c r="M15" s="12" t="n"/>
+      <c r="K15" s="28" t="n"/>
+      <c r="L15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -19276,16 +18498,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H16" s="12" t="inlineStr"/>
-      <c r="I16" s="27" t="inlineStr">
+      <c r="H16" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I16" s="12" t="n"/>
       <c r="J16" s="12" t="n"/>
-      <c r="K16" s="12" t="n"/>
-      <c r="L16" s="28" t="n"/>
-      <c r="M16" s="12" t="n"/>
+      <c r="K16" s="28" t="n"/>
+      <c r="L16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -19323,16 +18544,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H17" s="12" t="inlineStr"/>
-      <c r="I17" s="27" t="inlineStr">
+      <c r="H17" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I17" s="12" t="n"/>
       <c r="J17" s="12" t="n"/>
-      <c r="K17" s="12" t="n"/>
-      <c r="L17" s="28" t="n"/>
-      <c r="M17" s="12" t="n"/>
+      <c r="K17" s="28" t="n"/>
+      <c r="L17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -19370,16 +18590,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H18" s="12" t="inlineStr"/>
-      <c r="I18" s="27" t="inlineStr">
+      <c r="H18" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I18" s="12" t="n"/>
       <c r="J18" s="12" t="n"/>
-      <c r="K18" s="12" t="n"/>
-      <c r="L18" s="28" t="n"/>
-      <c r="M18" s="12" t="n"/>
+      <c r="K18" s="28" t="n"/>
+      <c r="L18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -19417,16 +18636,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H19" s="12" t="inlineStr"/>
-      <c r="I19" s="27" t="inlineStr">
+      <c r="H19" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I19" s="12" t="n"/>
       <c r="J19" s="12" t="n"/>
-      <c r="K19" s="12" t="n"/>
-      <c r="L19" s="28" t="n"/>
-      <c r="M19" s="12" t="n"/>
+      <c r="K19" s="28" t="n"/>
+      <c r="L19" s="12" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -19464,16 +18682,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H20" s="12" t="inlineStr"/>
-      <c r="I20" s="27" t="inlineStr">
+      <c r="H20" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I20" s="12" t="n"/>
       <c r="J20" s="12" t="n"/>
-      <c r="K20" s="12" t="n"/>
-      <c r="L20" s="28" t="n"/>
-      <c r="M20" s="12" t="n"/>
+      <c r="K20" s="28" t="n"/>
+      <c r="L20" s="12" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -19508,19 +18725,18 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>New Policy, Edit and the tag actions are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H21" s="12" t="inlineStr"/>
-      <c r="I21" s="27" t="inlineStr">
+          <t>New Policy, Edit and the tag actions are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H21" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I21" s="12" t="n"/>
       <c r="J21" s="12" t="n"/>
-      <c r="K21" s="12" t="n"/>
-      <c r="L21" s="28" t="n"/>
-      <c r="M21" s="12" t="n"/>
+      <c r="K21" s="28" t="n"/>
+      <c r="L21" s="12" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -19555,19 +18771,18 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>New Policy, Edit and the tag actions are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="inlineStr"/>
-      <c r="I22" s="27" t="inlineStr">
+          <t>New Policy, Edit and the tag actions are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H22" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I22" s="12" t="n"/>
       <c r="J22" s="12" t="n"/>
-      <c r="K22" s="12" t="n"/>
-      <c r="L22" s="28" t="n"/>
-      <c r="M22" s="12" t="n"/>
+      <c r="K22" s="28" t="n"/>
+      <c r="L22" s="12" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -19602,19 +18817,18 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>New Policy, Edit and the tag actions are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H23" s="12" t="inlineStr"/>
-      <c r="I23" s="27" t="inlineStr">
+          <t>New Policy, Edit and the tag actions are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H23" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I23" s="12" t="n"/>
       <c r="J23" s="12" t="n"/>
-      <c r="K23" s="12" t="n"/>
-      <c r="L23" s="28" t="n"/>
-      <c r="M23" s="12" t="n"/>
+      <c r="K23" s="28" t="n"/>
+      <c r="L23" s="12" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
@@ -19652,16 +18866,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H24" s="12" t="inlineStr"/>
-      <c r="I24" s="27" t="inlineStr">
+      <c r="H24" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I24" s="12" t="n"/>
       <c r="J24" s="12" t="n"/>
-      <c r="K24" s="12" t="n"/>
-      <c r="L24" s="28" t="n"/>
-      <c r="M24" s="12" t="n"/>
+      <c r="K24" s="28" t="n"/>
+      <c r="L24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -19699,16 +18912,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H25" s="12" t="inlineStr"/>
-      <c r="I25" s="27" t="inlineStr">
+      <c r="H25" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I25" s="12" t="n"/>
       <c r="J25" s="12" t="n"/>
-      <c r="K25" s="12" t="n"/>
-      <c r="L25" s="28" t="n"/>
-      <c r="M25" s="12" t="n"/>
+      <c r="K25" s="28" t="n"/>
+      <c r="L25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
@@ -19746,16 +18958,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H26" s="12" t="inlineStr"/>
-      <c r="I26" s="27" t="inlineStr">
+      <c r="H26" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I26" s="12" t="n"/>
       <c r="J26" s="12" t="n"/>
-      <c r="K26" s="12" t="n"/>
-      <c r="L26" s="28" t="n"/>
-      <c r="M26" s="12" t="n"/>
+      <c r="K26" s="28" t="n"/>
+      <c r="L26" s="12" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -19790,19 +19001,18 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>Upload &amp; Intake is not in the menu; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H27" s="12" t="inlineStr"/>
-      <c r="I27" s="27" t="inlineStr">
+          <t>Upload &amp; Intake is not in the menu; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H27" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I27" s="12" t="n"/>
       <c r="J27" s="12" t="n"/>
-      <c r="K27" s="12" t="n"/>
-      <c r="L27" s="28" t="n"/>
-      <c r="M27" s="12" t="n"/>
+      <c r="K27" s="28" t="n"/>
+      <c r="L27" s="12" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
@@ -19837,19 +19047,18 @@
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>Upload &amp; Intake is not in the menu; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H28" s="12" t="inlineStr"/>
-      <c r="I28" s="27" t="inlineStr">
+          <t>Upload &amp; Intake is not in the menu; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H28" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I28" s="12" t="n"/>
       <c r="J28" s="12" t="n"/>
-      <c r="K28" s="12" t="n"/>
-      <c r="L28" s="28" t="n"/>
-      <c r="M28" s="12" t="n"/>
+      <c r="K28" s="28" t="n"/>
+      <c r="L28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
@@ -19887,16 +19096,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H29" s="12" t="inlineStr"/>
-      <c r="I29" s="27" t="inlineStr">
+      <c r="H29" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I29" s="12" t="n"/>
       <c r="J29" s="12" t="n"/>
-      <c r="K29" s="12" t="n"/>
-      <c r="L29" s="28" t="n"/>
-      <c r="M29" s="12" t="n"/>
+      <c r="K29" s="28" t="n"/>
+      <c r="L29" s="12" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
@@ -19934,16 +19142,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H30" s="12" t="inlineStr"/>
-      <c r="I30" s="27" t="inlineStr">
+      <c r="H30" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I30" s="12" t="n"/>
       <c r="J30" s="12" t="n"/>
-      <c r="K30" s="12" t="n"/>
-      <c r="L30" s="28" t="n"/>
-      <c r="M30" s="12" t="n"/>
+      <c r="K30" s="28" t="n"/>
+      <c r="L30" s="12" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
@@ -19978,19 +19185,18 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>Run Processing and Re-assign Insurer are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H31" s="12" t="inlineStr"/>
-      <c r="I31" s="27" t="inlineStr">
+          <t>Run Processing and Re-assign Insurer are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H31" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I31" s="12" t="n"/>
       <c r="J31" s="12" t="n"/>
-      <c r="K31" s="12" t="n"/>
-      <c r="L31" s="28" t="n"/>
-      <c r="M31" s="12" t="n"/>
+      <c r="K31" s="28" t="n"/>
+      <c r="L31" s="12" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -20025,19 +19231,18 @@
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>Run Processing and Re-assign Insurer are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H32" s="12" t="inlineStr"/>
-      <c r="I32" s="27" t="inlineStr">
+          <t>Run Processing and Re-assign Insurer are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H32" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I32" s="12" t="n"/>
       <c r="J32" s="12" t="n"/>
-      <c r="K32" s="12" t="n"/>
-      <c r="L32" s="28" t="n"/>
-      <c r="M32" s="12" t="n"/>
+      <c r="K32" s="28" t="n"/>
+      <c r="L32" s="12" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
@@ -20075,16 +19280,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H33" s="12" t="inlineStr"/>
-      <c r="I33" s="27" t="inlineStr">
+      <c r="H33" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I33" s="12" t="n"/>
       <c r="J33" s="12" t="n"/>
-      <c r="K33" s="12" t="n"/>
-      <c r="L33" s="28" t="n"/>
-      <c r="M33" s="12" t="n"/>
+      <c r="K33" s="28" t="n"/>
+      <c r="L33" s="12" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
@@ -20122,16 +19326,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H34" s="12" t="inlineStr"/>
-      <c r="I34" s="27" t="inlineStr">
+      <c r="H34" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I34" s="12" t="n"/>
       <c r="J34" s="12" t="n"/>
-      <c r="K34" s="12" t="n"/>
-      <c r="L34" s="28" t="n"/>
-      <c r="M34" s="12" t="n"/>
+      <c r="K34" s="28" t="n"/>
+      <c r="L34" s="12" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
@@ -20166,19 +19369,18 @@
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>Submitted Policies Setup is read only or not in the menu; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H35" s="12" t="inlineStr"/>
-      <c r="I35" s="27" t="inlineStr">
+          <t>Submitted Policies Setup is read only or not in the menu; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H35" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I35" s="12" t="n"/>
       <c r="J35" s="12" t="n"/>
-      <c r="K35" s="12" t="n"/>
-      <c r="L35" s="28" t="n"/>
-      <c r="M35" s="12" t="n"/>
+      <c r="K35" s="28" t="n"/>
+      <c r="L35" s="12" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
@@ -20213,19 +19415,18 @@
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>Submitted Policies Setup is read only or not in the menu; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H36" s="12" t="inlineStr"/>
-      <c r="I36" s="27" t="inlineStr">
+          <t>Submitted Policies Setup is read only or not in the menu; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H36" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I36" s="12" t="n"/>
       <c r="J36" s="12" t="n"/>
-      <c r="K36" s="12" t="n"/>
-      <c r="L36" s="28" t="n"/>
-      <c r="M36" s="12" t="n"/>
+      <c r="K36" s="28" t="n"/>
+      <c r="L36" s="12" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
@@ -20263,16 +19464,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H37" s="12" t="inlineStr"/>
-      <c r="I37" s="27" t="inlineStr">
+      <c r="H37" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I37" s="12" t="n"/>
       <c r="J37" s="12" t="n"/>
-      <c r="K37" s="12" t="n"/>
-      <c r="L37" s="28" t="n"/>
-      <c r="M37" s="12" t="n"/>
+      <c r="K37" s="28" t="n"/>
+      <c r="L37" s="12" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
@@ -20307,19 +19507,18 @@
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>The rule set is not offered in My Approvals; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H38" s="12" t="inlineStr"/>
-      <c r="I38" s="27" t="inlineStr">
+          <t>The rule set is not offered in My Approvals; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H38" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I38" s="12" t="n"/>
       <c r="J38" s="12" t="n"/>
-      <c r="K38" s="12" t="n"/>
-      <c r="L38" s="28" t="n"/>
-      <c r="M38" s="12" t="n"/>
+      <c r="K38" s="28" t="n"/>
+      <c r="L38" s="12" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
@@ -20354,19 +19553,18 @@
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>The rule set is not offered in My Approvals; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H39" s="12" t="inlineStr"/>
-      <c r="I39" s="27" t="inlineStr">
+          <t>The rule set is not offered in My Approvals; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H39" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I39" s="12" t="n"/>
       <c r="J39" s="12" t="n"/>
-      <c r="K39" s="12" t="n"/>
-      <c r="L39" s="28" t="n"/>
-      <c r="M39" s="12" t="n"/>
+      <c r="K39" s="28" t="n"/>
+      <c r="L39" s="12" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
@@ -20404,16 +19602,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H40" s="12" t="inlineStr"/>
-      <c r="I40" s="27" t="inlineStr">
+      <c r="H40" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I40" s="12" t="n"/>
       <c r="J40" s="12" t="n"/>
-      <c r="K40" s="12" t="n"/>
-      <c r="L40" s="28" t="n"/>
-      <c r="M40" s="12" t="n"/>
+      <c r="K40" s="28" t="n"/>
+      <c r="L40" s="12" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
@@ -20451,16 +19648,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H41" s="12" t="inlineStr"/>
-      <c r="I41" s="27" t="inlineStr">
+      <c r="H41" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I41" s="12" t="n"/>
       <c r="J41" s="12" t="n"/>
-      <c r="K41" s="12" t="n"/>
-      <c r="L41" s="28" t="n"/>
-      <c r="M41" s="12" t="n"/>
+      <c r="K41" s="28" t="n"/>
+      <c r="L41" s="12" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
@@ -20498,16 +19694,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H42" s="12" t="inlineStr"/>
-      <c r="I42" s="27" t="inlineStr">
+      <c r="H42" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I42" s="12" t="n"/>
       <c r="J42" s="12" t="n"/>
-      <c r="K42" s="12" t="n"/>
-      <c r="L42" s="28" t="n"/>
-      <c r="M42" s="12" t="n"/>
+      <c r="K42" s="28" t="n"/>
+      <c r="L42" s="12" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
@@ -20542,19 +19737,18 @@
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>Generate IAAF is not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H43" s="12" t="inlineStr"/>
-      <c r="I43" s="27" t="inlineStr">
+          <t>Generate IAAF is not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H43" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I43" s="12" t="n"/>
       <c r="J43" s="12" t="n"/>
-      <c r="K43" s="12" t="n"/>
-      <c r="L43" s="28" t="n"/>
-      <c r="M43" s="12" t="n"/>
+      <c r="K43" s="28" t="n"/>
+      <c r="L43" s="12" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
@@ -20589,19 +19783,18 @@
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>Generate IAAF is not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H44" s="12" t="inlineStr"/>
-      <c r="I44" s="27" t="inlineStr">
+          <t>Generate IAAF is not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H44" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I44" s="12" t="n"/>
       <c r="J44" s="12" t="n"/>
-      <c r="K44" s="12" t="n"/>
-      <c r="L44" s="28" t="n"/>
-      <c r="M44" s="12" t="n"/>
+      <c r="K44" s="28" t="n"/>
+      <c r="L44" s="12" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
@@ -20639,16 +19832,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H45" s="12" t="inlineStr"/>
-      <c r="I45" s="27" t="inlineStr">
+      <c r="H45" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I45" s="12" t="n"/>
       <c r="J45" s="12" t="n"/>
-      <c r="K45" s="12" t="n"/>
-      <c r="L45" s="28" t="n"/>
-      <c r="M45" s="12" t="n"/>
+      <c r="K45" s="28" t="n"/>
+      <c r="L45" s="12" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
@@ -20686,16 +19878,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H46" s="12" t="inlineStr"/>
-      <c r="I46" s="27" t="inlineStr">
+      <c r="H46" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I46" s="12" t="n"/>
       <c r="J46" s="12" t="n"/>
-      <c r="K46" s="12" t="n"/>
-      <c r="L46" s="28" t="n"/>
-      <c r="M46" s="12" t="n"/>
+      <c r="K46" s="28" t="n"/>
+      <c r="L46" s="12" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
@@ -20730,19 +19921,18 @@
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>The IAAF is not offered in My Approvals; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H47" s="12" t="inlineStr"/>
-      <c r="I47" s="27" t="inlineStr">
+          <t>The IAAF is not offered in My Approvals; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H47" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I47" s="12" t="n"/>
       <c r="J47" s="12" t="n"/>
-      <c r="K47" s="12" t="n"/>
-      <c r="L47" s="28" t="n"/>
-      <c r="M47" s="12" t="n"/>
+      <c r="K47" s="28" t="n"/>
+      <c r="L47" s="12" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
@@ -20777,19 +19967,18 @@
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
-          <t>The IAAF is not offered in My Approvals; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H48" s="12" t="inlineStr"/>
-      <c r="I48" s="27" t="inlineStr">
+          <t>The IAAF is not offered in My Approvals; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H48" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I48" s="12" t="n"/>
       <c r="J48" s="12" t="n"/>
-      <c r="K48" s="12" t="n"/>
-      <c r="L48" s="28" t="n"/>
-      <c r="M48" s="12" t="n"/>
+      <c r="K48" s="28" t="n"/>
+      <c r="L48" s="12" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
@@ -20827,16 +20016,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H49" s="12" t="inlineStr"/>
-      <c r="I49" s="27" t="inlineStr">
+      <c r="H49" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I49" s="12" t="n"/>
       <c r="J49" s="12" t="n"/>
-      <c r="K49" s="12" t="n"/>
-      <c r="L49" s="28" t="n"/>
-      <c r="M49" s="12" t="n"/>
+      <c r="K49" s="28" t="n"/>
+      <c r="L49" s="12" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
@@ -20874,16 +20062,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H50" s="12" t="inlineStr"/>
-      <c r="I50" s="27" t="inlineStr">
+      <c r="H50" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I50" s="12" t="n"/>
       <c r="J50" s="12" t="n"/>
-      <c r="K50" s="12" t="n"/>
-      <c r="L50" s="28" t="n"/>
-      <c r="M50" s="12" t="n"/>
+      <c r="K50" s="28" t="n"/>
+      <c r="L50" s="12" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
@@ -20921,16 +20108,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H51" s="12" t="inlineStr"/>
-      <c r="I51" s="27" t="inlineStr">
+      <c r="H51" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I51" s="12" t="n"/>
       <c r="J51" s="12" t="n"/>
-      <c r="K51" s="12" t="n"/>
-      <c r="L51" s="28" t="n"/>
-      <c r="M51" s="12" t="n"/>
+      <c r="K51" s="28" t="n"/>
+      <c r="L51" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
@@ -20965,19 +20151,18 @@
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
-          <t>Generate TOR is not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H52" s="12" t="inlineStr"/>
-      <c r="I52" s="27" t="inlineStr">
+          <t>Generate TOR is not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H52" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I52" s="12" t="n"/>
       <c r="J52" s="12" t="n"/>
-      <c r="K52" s="12" t="n"/>
-      <c r="L52" s="28" t="n"/>
-      <c r="M52" s="12" t="n"/>
+      <c r="K52" s="28" t="n"/>
+      <c r="L52" s="12" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
@@ -21012,19 +20197,18 @@
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>Generate TOR is not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H53" s="12" t="inlineStr"/>
-      <c r="I53" s="27" t="inlineStr">
+          <t>Generate TOR is not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H53" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I53" s="12" t="n"/>
       <c r="J53" s="12" t="n"/>
-      <c r="K53" s="12" t="n"/>
-      <c r="L53" s="28" t="n"/>
-      <c r="M53" s="12" t="n"/>
+      <c r="K53" s="28" t="n"/>
+      <c r="L53" s="12" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
@@ -21062,16 +20246,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H54" s="12" t="inlineStr"/>
-      <c r="I54" s="27" t="inlineStr">
+      <c r="H54" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I54" s="12" t="n"/>
       <c r="J54" s="12" t="n"/>
-      <c r="K54" s="12" t="n"/>
-      <c r="L54" s="28" t="n"/>
-      <c r="M54" s="12" t="n"/>
+      <c r="K54" s="28" t="n"/>
+      <c r="L54" s="12" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
@@ -21106,19 +20289,18 @@
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>The TOR is not offered in My Approvals; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H55" s="12" t="inlineStr"/>
-      <c r="I55" s="27" t="inlineStr">
+          <t>The TOR is not offered in My Approvals; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H55" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I55" s="12" t="n"/>
       <c r="J55" s="12" t="n"/>
-      <c r="K55" s="12" t="n"/>
-      <c r="L55" s="28" t="n"/>
-      <c r="M55" s="12" t="n"/>
+      <c r="K55" s="28" t="n"/>
+      <c r="L55" s="12" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
@@ -21153,19 +20335,18 @@
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
-          <t>The TOR is not offered in My Approvals; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H56" s="12" t="inlineStr"/>
-      <c r="I56" s="27" t="inlineStr">
+          <t>The TOR is not offered in My Approvals; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H56" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I56" s="12" t="n"/>
       <c r="J56" s="12" t="n"/>
-      <c r="K56" s="12" t="n"/>
-      <c r="L56" s="28" t="n"/>
-      <c r="M56" s="12" t="n"/>
+      <c r="K56" s="28" t="n"/>
+      <c r="L56" s="12" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
@@ -21203,16 +20384,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H57" s="12" t="inlineStr"/>
-      <c r="I57" s="27" t="inlineStr">
+      <c r="H57" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I57" s="12" t="n"/>
       <c r="J57" s="12" t="n"/>
-      <c r="K57" s="12" t="n"/>
-      <c r="L57" s="28" t="n"/>
-      <c r="M57" s="12" t="n"/>
+      <c r="K57" s="28" t="n"/>
+      <c r="L57" s="12" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
@@ -21250,16 +20430,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H58" s="12" t="inlineStr"/>
-      <c r="I58" s="27" t="inlineStr">
+      <c r="H58" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I58" s="12" t="n"/>
       <c r="J58" s="12" t="n"/>
-      <c r="K58" s="12" t="n"/>
-      <c r="L58" s="28" t="n"/>
-      <c r="M58" s="12" t="n"/>
+      <c r="K58" s="28" t="n"/>
+      <c r="L58" s="12" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
@@ -21294,19 +20473,18 @@
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t>Letters &amp; Print Batches actions are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H59" s="12" t="inlineStr"/>
-      <c r="I59" s="27" t="inlineStr">
+          <t>Letters &amp; Print Batches actions are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H59" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I59" s="12" t="n"/>
       <c r="J59" s="12" t="n"/>
-      <c r="K59" s="12" t="n"/>
-      <c r="L59" s="28" t="n"/>
-      <c r="M59" s="12" t="n"/>
+      <c r="K59" s="28" t="n"/>
+      <c r="L59" s="12" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
@@ -21341,19 +20519,18 @@
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
-          <t>Letters &amp; Print Batches actions are not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H60" s="12" t="inlineStr"/>
-      <c r="I60" s="27" t="inlineStr">
+          <t>Letters &amp; Print Batches actions are not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H60" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I60" s="12" t="n"/>
       <c r="J60" s="12" t="n"/>
-      <c r="K60" s="12" t="n"/>
-      <c r="L60" s="28" t="n"/>
-      <c r="M60" s="12" t="n"/>
+      <c r="K60" s="28" t="n"/>
+      <c r="L60" s="12" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
@@ -21391,16 +20568,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H61" s="12" t="inlineStr"/>
-      <c r="I61" s="27" t="inlineStr">
+      <c r="H61" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I61" s="12" t="n"/>
       <c r="J61" s="12" t="n"/>
-      <c r="K61" s="12" t="n"/>
-      <c r="L61" s="28" t="n"/>
-      <c r="M61" s="12" t="n"/>
+      <c r="K61" s="28" t="n"/>
+      <c r="L61" s="12" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -21438,16 +20614,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H62" s="12" t="inlineStr"/>
-      <c r="I62" s="27" t="inlineStr">
+      <c r="H62" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I62" s="12" t="n"/>
       <c r="J62" s="12" t="n"/>
-      <c r="K62" s="12" t="n"/>
-      <c r="L62" s="28" t="n"/>
-      <c r="M62" s="12" t="n"/>
+      <c r="K62" s="28" t="n"/>
+      <c r="L62" s="12" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
@@ -21482,19 +20657,18 @@
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
-          <t>Handling Fees is not in the menu; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H63" s="12" t="inlineStr"/>
-      <c r="I63" s="27" t="inlineStr">
+          <t>Handling Fees is not in the menu; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H63" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I63" s="12" t="n"/>
       <c r="J63" s="12" t="n"/>
-      <c r="K63" s="12" t="n"/>
-      <c r="L63" s="28" t="n"/>
-      <c r="M63" s="12" t="n"/>
+      <c r="K63" s="28" t="n"/>
+      <c r="L63" s="12" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
@@ -21529,19 +20703,18 @@
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
-          <t>Handling Fees is not in the menu; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H64" s="12" t="inlineStr"/>
-      <c r="I64" s="27" t="inlineStr">
+          <t>Handling Fees is not in the menu; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H64" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I64" s="12" t="n"/>
       <c r="J64" s="12" t="n"/>
-      <c r="K64" s="12" t="n"/>
-      <c r="L64" s="28" t="n"/>
-      <c r="M64" s="12" t="n"/>
+      <c r="K64" s="28" t="n"/>
+      <c r="L64" s="12" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
@@ -21579,16 +20752,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H65" s="12" t="inlineStr"/>
-      <c r="I65" s="27" t="inlineStr">
+      <c r="H65" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I65" s="12" t="n"/>
       <c r="J65" s="12" t="n"/>
-      <c r="K65" s="12" t="n"/>
-      <c r="L65" s="28" t="n"/>
-      <c r="M65" s="12" t="n"/>
+      <c r="K65" s="28" t="n"/>
+      <c r="L65" s="12" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
@@ -21623,19 +20795,18 @@
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
-          <t>The Migration upload is not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H66" s="12" t="inlineStr"/>
-      <c r="I66" s="27" t="inlineStr">
+          <t>The Migration upload is not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H66" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I66" s="12" t="n"/>
       <c r="J66" s="12" t="n"/>
-      <c r="K66" s="12" t="n"/>
-      <c r="L66" s="28" t="n"/>
-      <c r="M66" s="12" t="n"/>
+      <c r="K66" s="28" t="n"/>
+      <c r="L66" s="12" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
@@ -21670,19 +20841,18 @@
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
-          <t>The Migration upload is not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H67" s="12" t="inlineStr"/>
-      <c r="I67" s="27" t="inlineStr">
+          <t>The Migration upload is not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H67" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I67" s="12" t="n"/>
       <c r="J67" s="12" t="n"/>
-      <c r="K67" s="12" t="n"/>
-      <c r="L67" s="28" t="n"/>
-      <c r="M67" s="12" t="n"/>
+      <c r="K67" s="28" t="n"/>
+      <c r="L67" s="12" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
@@ -21720,16 +20890,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H68" s="12" t="inlineStr"/>
-      <c r="I68" s="27" t="inlineStr">
+      <c r="H68" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I68" s="12" t="n"/>
       <c r="J68" s="12" t="n"/>
-      <c r="K68" s="12" t="n"/>
-      <c r="L68" s="28" t="n"/>
-      <c r="M68" s="12" t="n"/>
+      <c r="K68" s="28" t="n"/>
+      <c r="L68" s="12" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
@@ -21767,16 +20936,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H69" s="12" t="inlineStr"/>
-      <c r="I69" s="27" t="inlineStr">
+      <c r="H69" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I69" s="12" t="n"/>
       <c r="J69" s="12" t="n"/>
-      <c r="K69" s="12" t="n"/>
-      <c r="L69" s="28" t="n"/>
-      <c r="M69" s="12" t="n"/>
+      <c r="K69" s="28" t="n"/>
+      <c r="L69" s="12" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
@@ -21814,16 +20982,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H70" s="12" t="inlineStr"/>
-      <c r="I70" s="27" t="inlineStr">
+      <c r="H70" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I70" s="12" t="n"/>
       <c r="J70" s="12" t="n"/>
-      <c r="K70" s="12" t="n"/>
-      <c r="L70" s="28" t="n"/>
-      <c r="M70" s="12" t="n"/>
+      <c r="K70" s="28" t="n"/>
+      <c r="L70" s="12" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
@@ -21858,19 +21025,18 @@
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>Export is not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H71" s="12" t="inlineStr"/>
-      <c r="I71" s="27" t="inlineStr">
+          <t>Export is not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H71" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I71" s="12" t="n"/>
       <c r="J71" s="12" t="n"/>
-      <c r="K71" s="12" t="n"/>
-      <c r="L71" s="28" t="n"/>
-      <c r="M71" s="12" t="n"/>
+      <c r="K71" s="28" t="n"/>
+      <c r="L71" s="12" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
@@ -21905,19 +21071,18 @@
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
-          <t>Export is not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H72" s="12" t="inlineStr"/>
-      <c r="I72" s="27" t="inlineStr">
+          <t>Export is not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H72" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I72" s="12" t="n"/>
       <c r="J72" s="12" t="n"/>
-      <c r="K72" s="12" t="n"/>
-      <c r="L72" s="28" t="n"/>
-      <c r="M72" s="12" t="n"/>
+      <c r="K72" s="28" t="n"/>
+      <c r="L72" s="12" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
@@ -21952,19 +21117,18 @@
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
-          <t>Export is not shown; the call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H73" s="12" t="inlineStr"/>
-      <c r="I73" s="27" t="inlineStr">
+          <t>Export is not shown; the request is refused.</t>
+        </is>
+      </c>
+      <c r="H73" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I73" s="12" t="n"/>
       <c r="J73" s="12" t="n"/>
-      <c r="K73" s="12" t="n"/>
-      <c r="L73" s="28" t="n"/>
-      <c r="M73" s="12" t="n"/>
+      <c r="K73" s="28" t="n"/>
+      <c r="L73" s="12" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
@@ -22002,16 +21166,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H74" s="12" t="inlineStr"/>
-      <c r="I74" s="27" t="inlineStr">
+      <c r="H74" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I74" s="12" t="n"/>
       <c r="J74" s="12" t="n"/>
-      <c r="K74" s="12" t="n"/>
-      <c r="L74" s="28" t="n"/>
-      <c r="M74" s="12" t="n"/>
+      <c r="K74" s="28" t="n"/>
+      <c r="L74" s="12" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
@@ -22049,16 +21212,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H75" s="12" t="inlineStr"/>
-      <c r="I75" s="27" t="inlineStr">
+      <c r="H75" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I75" s="12" t="n"/>
       <c r="J75" s="12" t="n"/>
-      <c r="K75" s="12" t="n"/>
-      <c r="L75" s="28" t="n"/>
-      <c r="M75" s="12" t="n"/>
+      <c r="K75" s="28" t="n"/>
+      <c r="L75" s="12" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
@@ -22096,16 +21258,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H76" s="12" t="inlineStr"/>
-      <c r="I76" s="27" t="inlineStr">
+      <c r="H76" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I76" s="12" t="n"/>
       <c r="J76" s="12" t="n"/>
-      <c r="K76" s="12" t="n"/>
-      <c r="L76" s="28" t="n"/>
-      <c r="M76" s="12" t="n"/>
+      <c r="K76" s="28" t="n"/>
+      <c r="L76" s="12" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
@@ -22143,16 +21304,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H77" s="12" t="inlineStr"/>
-      <c r="I77" s="27" t="inlineStr">
+      <c r="H77" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I77" s="12" t="n"/>
       <c r="J77" s="12" t="n"/>
-      <c r="K77" s="12" t="n"/>
-      <c r="L77" s="28" t="n"/>
-      <c r="M77" s="12" t="n"/>
+      <c r="K77" s="28" t="n"/>
+      <c r="L77" s="12" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
@@ -22190,16 +21350,15 @@
           <t>The action is offered and completes.</t>
         </is>
       </c>
-      <c r="H78" s="12" t="inlineStr"/>
-      <c r="I78" s="27" t="inlineStr">
+      <c r="H78" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I78" s="12" t="n"/>
       <c r="J78" s="12" t="n"/>
-      <c r="K78" s="12" t="n"/>
-      <c r="L78" s="28" t="n"/>
-      <c r="M78" s="12" t="n"/>
+      <c r="K78" s="28" t="n"/>
+      <c r="L78" s="12" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
@@ -22234,19 +21393,18 @@
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
-          <t>The Submitted Policies category is not listed; the run call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H79" s="12" t="inlineStr"/>
-      <c r="I79" s="27" t="inlineStr">
+          <t>The Submitted Policies category is not listed; a direct run request is refused.</t>
+        </is>
+      </c>
+      <c r="H79" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I79" s="12" t="n"/>
       <c r="J79" s="12" t="n"/>
-      <c r="K79" s="12" t="n"/>
-      <c r="L79" s="28" t="n"/>
-      <c r="M79" s="12" t="n"/>
+      <c r="K79" s="28" t="n"/>
+      <c r="L79" s="12" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
@@ -22281,19 +21439,18 @@
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
-          <t>The Submitted Policies category is not listed; the run call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H80" s="12" t="inlineStr"/>
-      <c r="I80" s="27" t="inlineStr">
+          <t>The Submitted Policies category is not listed; a direct run request is refused.</t>
+        </is>
+      </c>
+      <c r="H80" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I80" s="12" t="n"/>
       <c r="J80" s="12" t="n"/>
-      <c r="K80" s="12" t="n"/>
-      <c r="L80" s="28" t="n"/>
-      <c r="M80" s="12" t="n"/>
+      <c r="K80" s="28" t="n"/>
+      <c r="L80" s="12" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
@@ -22328,26 +21485,25 @@
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
-          <t>The Submitted Policies category is not listed; the run call returns HTTP 403.</t>
-        </is>
-      </c>
-      <c r="H81" s="12" t="inlineStr"/>
-      <c r="I81" s="27" t="inlineStr">
+          <t>The Submitted Policies category is not listed; a direct run request is refused.</t>
+        </is>
+      </c>
+      <c r="H81" s="27" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
+      <c r="I81" s="12" t="n"/>
       <c r="J81" s="12" t="n"/>
-      <c r="K81" s="12" t="n"/>
-      <c r="L81" s="28" t="n"/>
-      <c r="M81" s="12" t="n"/>
+      <c r="K81" s="28" t="n"/>
+      <c r="L81" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M81"/>
+  <autoFilter ref="A4:L81"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A2:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="I5:I581">
+  <conditionalFormatting sqref="H5:H581">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"Pass"</formula>
     </cfRule>
@@ -22361,7 +21517,7 @@
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:M581">
+  <conditionalFormatting sqref="A5:L581">
     <cfRule type="expression" priority="5" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -22370,7 +21526,7 @@
     <dataValidation sqref="F5:F581" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Access" error="Choose a value from the list (Access)." type="list">
       <formula1>'_lists'!$F$1:$F$2</formula1>
     </dataValidation>
-    <dataValidation sqref="I5:I581" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
+    <dataValidation sqref="H5:H581" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
       <formula1>'_lists'!$G$1:$G$5</formula1>
     </dataValidation>
   </dataValidations>
